--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>10100</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8654.3706289841193</v>
+        <v>8286.8450875198287</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1345.6293710158807</v>
+        <v>1713.1549124801713</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1427,143 +1427,153 @@
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46200</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
+      <c r="D21" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E21" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
+        <v>26.951284766785516</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>73.04871523321448</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>8581.3219137509041</v>
+      </c>
+      <c r="H21" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1418.6780862490959</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46201</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
+      <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E22" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
+        <v>26.723797776627652</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>73.276202223372351</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>8508.0457115275312</v>
+      </c>
+      <c r="H22" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1491.9542884724688</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A23" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B23" s="24">
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="21" t="str">
+      <c r="D23" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E23" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H23" s="21" t="str">
+        <v>26.49560235059209</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="5"/>
+        <v>73.504397649407906</v>
+      </c>
+      <c r="G23" s="21">
+        <f t="shared" si="4"/>
+        <v>8434.5413138781241</v>
+      </c>
+      <c r="H23" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1565.4586861218759</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A24" s="2">
+        <v>46203</v>
+      </c>
+      <c r="B24" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
+      <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E24" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
+        <v>26.266696282480613</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="5"/>
+        <v>73.733303717519391</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="4"/>
+        <v>8360.8080101606047</v>
+      </c>
+      <c r="H24" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1639.1919898393953</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A25" s="19">
+        <v>46204</v>
+      </c>
+      <c r="B25" s="24">
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="21" t="str">
+      <c r="D25" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E25" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H25" s="21" t="str">
+        <v>26.03707735922449</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="5"/>
+        <v>73.962922640775503</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="4"/>
+        <v>8286.8450875198287</v>
+      </c>
+      <c r="H25" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1713.1549124801713</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>9600</v>
+        <v>9100</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8286.8450875198287</v>
+        <v>7913.561084752052</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1713.1549124801713</v>
+        <v>2086.438915247948</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1577,143 +1577,153 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A26" s="2">
+        <v>46205</v>
+      </c>
+      <c r="B26" s="23">
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E26" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E26" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
+        <v>25.806743360863102</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="5"/>
+        <v>74.193256639136905</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="4"/>
+        <v>8212.6518308806917</v>
+      </c>
+      <c r="H26" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1787.3481691193083</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A27" s="19">
+        <v>46207</v>
+      </c>
+      <c r="B27" s="24">
+        <f t="shared" si="3"/>
+        <v>26</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="21" t="str">
+      <c r="D27" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E27" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G27" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
+        <v>25.575692060522467</v>
+      </c>
+      <c r="F27" s="21">
+        <f t="shared" si="5"/>
+        <v>74.424307939477529</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="4"/>
+        <v>8138.2275229412144</v>
+      </c>
+      <c r="H27" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1861.7724770587856</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A28" s="2">
+        <v>46208</v>
+      </c>
+      <c r="B28" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="4" t="str">
+      <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E28" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
+        <v>25.343921224393711</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="5"/>
+        <v>74.656078775606289</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="4"/>
+        <v>8063.5714441656082</v>
+      </c>
+      <c r="H28" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1936.4285558343918</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A29" s="19">
+        <v>46209</v>
+      </c>
+      <c r="B29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="21" t="str">
+      <c r="D29" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E29" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H29" s="21" t="str">
+        <v>25.111428611711474</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>74.888571388288526</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="4"/>
+        <v>7988.68287277732</v>
+      </c>
+      <c r="H29" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2011.31712722268</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A30" s="2">
+        <v>46210</v>
+      </c>
+      <c r="B30" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="4" t="str">
+      <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E30" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
+        <v>24.878211974732245</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="5"/>
+        <v>75.121788025267762</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>7913.561084752052</v>
+      </c>
+      <c r="H30" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2086.438915247948</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>9100</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>7913.561084752052</v>
+        <v>7381.1172094286358</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2086.438915247948</v>
+        <v>2618.8827905713642</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1727,199 +1727,213 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A31" s="19">
+        <v>46212</v>
+      </c>
+      <c r="B31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="C31" s="20"/>
-      <c r="D31" s="21" t="str">
+      <c r="D31" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E31" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E31" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H31" s="21" t="str">
+        <v>24.644269058712624</v>
+      </c>
+      <c r="F31" s="21">
+        <f t="shared" si="5"/>
+        <v>75.355730941287376</v>
+      </c>
+      <c r="G31" s="21">
+        <f t="shared" si="4"/>
+        <v>7838.2053538107648</v>
+      </c>
+      <c r="H31" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2161.7946461892352</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A32" s="2">
+        <v>46212</v>
+      </c>
+      <c r="B32" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4" t="str">
+      <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E32" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E32" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
+        <v>24.409597601887544</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="5"/>
+        <v>75.59040239811246</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="4"/>
+        <v>7762.6149514126528</v>
+      </c>
+      <c r="H32" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2237.3850485873472</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A33" s="19">
+        <v>46212</v>
+      </c>
+      <c r="B33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="C33" s="20"/>
-      <c r="D33" s="21" t="str">
+      <c r="D33" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E33" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E33" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H33" s="21" t="str">
+        <v>24.174195335448374</v>
+      </c>
+      <c r="F33" s="21">
+        <f t="shared" si="5"/>
+        <v>75.825804664551626</v>
+      </c>
+      <c r="G33" s="21">
+        <f t="shared" si="4"/>
+        <v>7686.7891467481013</v>
+      </c>
+      <c r="H33" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2313.2108532518987</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A34" s="2">
+        <v>46214</v>
+      </c>
+      <c r="B34" s="23">
+        <f t="shared" si="3"/>
+        <v>33</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="4">
         <f t="shared" ref="D34:D65" si="6">IF(AND($A34&lt;&gt;"",$B34&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E34" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F34" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="str">
+        <v>23.938059983521015</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="5"/>
+        <v>76.061940016478985</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="4"/>
+        <v>7610.7272067316226</v>
+      </c>
+      <c r="H34" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2389.2727932683774</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A35" s="19">
+        <v>46214</v>
+      </c>
+      <c r="B35" s="24">
+        <f t="shared" si="3"/>
+        <v>34</v>
       </c>
       <c r="C35" s="20"/>
-      <c r="D35" s="21" t="str">
+      <c r="D35" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E35" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E35" s="21">
         <f t="shared" ref="E35:E66" si="7">IF(AND($A35&lt;&gt;"",$B35&lt;&gt;""),G34*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H35" s="21" t="str">
+        <v>23.701189263143871</v>
+      </c>
+      <c r="F35" s="21">
+        <f t="shared" si="5"/>
+        <v>76.298810736856126</v>
+      </c>
+      <c r="G35" s="21">
+        <f t="shared" si="4"/>
+        <v>7534.4283959947661</v>
+      </c>
+      <c r="H35" s="21">
         <f t="shared" ref="H35:H66" si="8">IF(AND($A35&lt;&gt;"",$B35&lt;&gt;""),$K$7-G35,"")</f>
-        <v/>
+        <v>2465.5716040052339</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A36" s="2">
+        <v>46214</v>
+      </c>
+      <c r="B36" s="23">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="4" t="str">
+      <c r="D36" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E36" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E36" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F36" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G36" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H36" s="4" t="str">
+        <v>23.463580884245786</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="5"/>
+        <v>76.536419115754214</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="4"/>
+        <v>7457.891976879012</v>
+      </c>
+      <c r="H36" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2542.108023120988</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
-      <c r="B37" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A37" s="19">
+        <v>46215</v>
+      </c>
+      <c r="B37" s="24">
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
       <c r="C37" s="20"/>
-      <c r="D37" s="21" t="str">
+      <c r="D37" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E37" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E37" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F37" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G37" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H37" s="21" t="str">
+        <v>23.225232549623925</v>
+      </c>
+      <c r="F37" s="21">
+        <f t="shared" si="5"/>
+        <v>76.774767450376075</v>
+      </c>
+      <c r="G37" s="21">
+        <f t="shared" si="4"/>
+        <v>7381.1172094286358</v>
+      </c>
+      <c r="H37" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2618.8827905713642</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>8400</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>7381.1172094286358</v>
+        <v>6679.2953882620041</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2618.8827905713642</v>
+        <v>3320.7046117379959</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1937,255 +1937,273 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A38" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B38" s="23">
+        <f t="shared" si="3"/>
+        <v>37</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="4" t="str">
+      <c r="D38" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E38" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E38" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F38" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G38" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H38" s="4" t="str">
+        <v>22.986141954921521</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="5"/>
+        <v>77.013858045078479</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="4"/>
+        <v>7304.1033513835573</v>
+      </c>
+      <c r="H38" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2695.8966486164427</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A39" s="19">
+        <v>46217</v>
+      </c>
+      <c r="B39" s="24">
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="C39" s="20"/>
-      <c r="D39" s="21" t="str">
+      <c r="D39" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E39" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E39" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F39" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G39" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H39" s="21" t="str">
+        <v>22.746306788605636</v>
+      </c>
+      <c r="F39" s="21">
+        <f t="shared" si="5"/>
+        <v>77.253693211394364</v>
+      </c>
+      <c r="G39" s="21">
+        <f t="shared" si="4"/>
+        <v>7226.8496581721629</v>
+      </c>
+      <c r="H39" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2773.1503418278371</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B40" s="23">
+        <f t="shared" si="3"/>
+        <v>39</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="4" t="str">
+      <c r="D40" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E40" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E40" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F40" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G40" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H40" s="4" t="str">
+        <v>22.505724731944795</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="5"/>
+        <v>77.494275268055205</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="4"/>
+        <v>7149.3553829041075</v>
+      </c>
+      <c r="H40" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2850.6446170958925</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A41" s="19">
+        <v>46220</v>
+      </c>
+      <c r="B41" s="24">
+        <f t="shared" si="3"/>
+        <v>40</v>
       </c>
       <c r="C41" s="20"/>
-      <c r="D41" s="21" t="str">
+      <c r="D41" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E41" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E41" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F41" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G41" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H41" s="21" t="str">
+        <v>22.264393458986568</v>
+      </c>
+      <c r="F41" s="21">
+        <f t="shared" si="5"/>
+        <v>77.735606541013425</v>
+      </c>
+      <c r="G41" s="21">
+        <f t="shared" si="4"/>
+        <v>7071.6197763630944</v>
+      </c>
+      <c r="H41" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2928.3802236369056</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A42" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B42" s="23">
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="4" t="str">
+      <c r="D42" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E42" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E42" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F42" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H42" s="4" t="str">
+        <v>22.022310636535092</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="5"/>
+        <v>77.977689363464904</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="4"/>
+        <v>6993.6420869996291</v>
+      </c>
+      <c r="H42" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3006.3579130003709</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A43" s="19">
+        <v>46223</v>
+      </c>
+      <c r="B43" s="24">
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
       <c r="C43" s="20"/>
-      <c r="D43" s="21" t="str">
+      <c r="D43" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E43" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E43" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F43" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G43" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H43" s="21" t="str">
+        <v>21.779473924128496</v>
+      </c>
+      <c r="F43" s="21">
+        <f t="shared" si="5"/>
+        <v>78.220526075871504</v>
+      </c>
+      <c r="G43" s="21">
+        <f t="shared" si="4"/>
+        <v>6915.4215609237572</v>
+      </c>
+      <c r="H43" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3084.5784390762428</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A44" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B44" s="23">
+        <f t="shared" si="3"/>
+        <v>43</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="4" t="str">
+      <c r="D44" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E44" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E44" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F44" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G44" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H44" s="4" t="str">
+        <v>21.535880974016301</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" si="5"/>
+        <v>78.464119025983706</v>
+      </c>
+      <c r="G44" s="4">
+        <f t="shared" si="4"/>
+        <v>6836.9574418977736</v>
+      </c>
+      <c r="H44" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3163.0425581022264</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A45" s="19">
+        <v>46224</v>
+      </c>
+      <c r="B45" s="24">
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="C45" s="20"/>
-      <c r="D45" s="21" t="str">
+      <c r="D45" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E45" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E45" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F45" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G45" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H45" s="21" t="str">
+        <v>21.291529431136691</v>
+      </c>
+      <c r="F45" s="21">
+        <f t="shared" si="5"/>
+        <v>78.708470568863305</v>
+      </c>
+      <c r="G45" s="21">
+        <f t="shared" si="4"/>
+        <v>6758.2489713289106</v>
+      </c>
+      <c r="H45" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3241.7510286710894</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A46" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B46" s="23">
+        <f t="shared" si="3"/>
+        <v>45</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="4" t="str">
+      <c r="D46" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E46" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E46" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F46" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G46" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H46" s="4" t="str">
+        <v>21.04641693309377</v>
+      </c>
+      <c r="F46" s="4">
+        <f t="shared" si="5"/>
+        <v>78.953583066906234</v>
+      </c>
+      <c r="G46" s="4">
+        <f t="shared" si="4"/>
+        <v>6679.2953882620041</v>
+      </c>
+      <c r="H46" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3320.7046117379959</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>7500</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>6679.2953882620041</v>
+        <v>5382.0725484424574</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3320.7046117379959</v>
+        <v>4617.9274515575426</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2207,451 +2207,483 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
-      <c r="B47" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A47" s="19">
+        <v>46226</v>
+      </c>
+      <c r="B47" s="24">
+        <f t="shared" si="3"/>
+        <v>46</v>
       </c>
       <c r="C47" s="20"/>
-      <c r="D47" s="21" t="str">
+      <c r="D47" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E47" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E47" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F47" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G47" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H47" s="21" t="str">
+        <v>20.800541110134702</v>
+      </c>
+      <c r="F47" s="21">
+        <f t="shared" si="5"/>
+        <v>79.199458889865298</v>
+      </c>
+      <c r="G47" s="21">
+        <f t="shared" si="4"/>
+        <v>6600.0959293721389</v>
+      </c>
+      <c r="H47" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3399.9040706278611</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A48" s="2">
+        <v>46228</v>
+      </c>
+      <c r="B48" s="23">
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="4" t="str">
+      <c r="D48" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E48" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E48" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F48" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G48" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H48" s="4" t="str">
+        <v>20.553899585126821</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="5"/>
+        <v>79.446100414873172</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="4"/>
+        <v>6520.6498289572655</v>
+      </c>
+      <c r="H48" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3479.3501710427345</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
-      <c r="B49" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A49" s="19">
+        <v>46228</v>
+      </c>
+      <c r="B49" s="24">
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="C49" s="20"/>
-      <c r="D49" s="21" t="str">
+      <c r="D49" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E49" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E49" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F49" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G49" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H49" s="21" t="str">
+        <v>20.306489973534621</v>
+      </c>
+      <c r="F49" s="21">
+        <f t="shared" si="5"/>
+        <v>79.693510026465376</v>
+      </c>
+      <c r="G49" s="21">
+        <f t="shared" si="4"/>
+        <v>6440.9563189308001</v>
+      </c>
+      <c r="H49" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3559.0436810691999</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A50" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B50" s="23">
+        <f t="shared" si="3"/>
+        <v>49</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="4" t="str">
+      <c r="D50" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E50" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E50" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F50" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G50" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H50" s="4" t="str">
+        <v>20.058309883396735</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" si="5"/>
+        <v>79.941690116603269</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="4"/>
+        <v>6361.0146288141968</v>
+      </c>
+      <c r="H50" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3638.9853711858032</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A51" s="19">
+        <v>46230</v>
+      </c>
+      <c r="B51" s="24">
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="C51" s="20"/>
-      <c r="D51" s="21" t="str">
+      <c r="D51" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E51" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E51" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F51" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G51" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H51" s="21" t="str">
+        <v>19.809356915302786</v>
+      </c>
+      <c r="F51" s="21">
+        <f t="shared" si="5"/>
+        <v>80.190643084697214</v>
+      </c>
+      <c r="G51" s="21">
+        <f t="shared" si="4"/>
+        <v>6280.8239857294993</v>
+      </c>
+      <c r="H51" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3719.1760142705007</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A52" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="23">
+        <f t="shared" si="3"/>
+        <v>51</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="4" t="str">
+      <c r="D52" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E52" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E52" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F52" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G52" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H52" s="4" t="str">
+        <v>19.559628662370194</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="5"/>
+        <v>80.440371337629813</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="4"/>
+        <v>6200.3836143918697</v>
+      </c>
+      <c r="H52" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3799.6163856081303</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
-      <c r="B53" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A53" s="19">
+        <v>46232</v>
+      </c>
+      <c r="B53" s="24">
+        <f t="shared" si="3"/>
+        <v>52</v>
       </c>
       <c r="C53" s="20"/>
-      <c r="D53" s="21" t="str">
+      <c r="D53" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E53" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E53" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F53" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G53" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H53" s="21" t="str">
+        <v>19.309122710220915</v>
+      </c>
+      <c r="F53" s="21">
+        <f t="shared" si="5"/>
+        <v>80.690877289779081</v>
+      </c>
+      <c r="G53" s="21">
+        <f t="shared" si="4"/>
+        <v>6119.6927371020911</v>
+      </c>
+      <c r="H53" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3880.3072628979089</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="2"/>
-      <c r="B54" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A54" s="2">
+        <v>46233</v>
+      </c>
+      <c r="B54" s="23">
+        <f t="shared" si="3"/>
+        <v>53</v>
       </c>
       <c r="C54" s="3"/>
-      <c r="D54" s="4" t="str">
+      <c r="D54" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E54" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E54" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F54" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G54" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H54" s="4" t="str">
+        <v>19.057836636958086</v>
+      </c>
+      <c r="F54" s="4">
+        <f t="shared" si="5"/>
+        <v>80.942163363041914</v>
+      </c>
+      <c r="G54" s="4">
+        <f t="shared" si="4"/>
+        <v>6038.7505737390493</v>
+      </c>
+      <c r="H54" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3961.2494262609507</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="19"/>
-      <c r="B55" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A55" s="19">
+        <v>46234</v>
+      </c>
+      <c r="B55" s="24">
+        <f t="shared" si="3"/>
+        <v>54</v>
       </c>
       <c r="C55" s="20"/>
-      <c r="D55" s="21" t="str">
+      <c r="D55" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E55" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E55" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F55" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G55" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H55" s="21" t="str">
+        <v>18.805768013142622</v>
+      </c>
+      <c r="F55" s="21">
+        <f t="shared" si="5"/>
+        <v>81.194231986857375</v>
+      </c>
+      <c r="G55" s="21">
+        <f t="shared" si="4"/>
+        <v>5957.5563417521917</v>
+      </c>
+      <c r="H55" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>4042.4436582478083</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A56" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B56" s="23">
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="4" t="str">
+      <c r="D56" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E56" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E56" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F56" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G56" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H56" s="4" t="str">
+        <v>18.552914401769716</v>
+      </c>
+      <c r="F56" s="4">
+        <f t="shared" si="5"/>
+        <v>81.447085598230288</v>
+      </c>
+      <c r="G56" s="4">
+        <f t="shared" si="4"/>
+        <v>5876.1092561539617</v>
+      </c>
+      <c r="H56" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>4123.8907438460383</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
-      <c r="B57" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A57" s="19">
+        <v>46236</v>
+      </c>
+      <c r="B57" s="24">
+        <f t="shared" si="3"/>
+        <v>56</v>
       </c>
       <c r="C57" s="20"/>
-      <c r="D57" s="21" t="str">
+      <c r="D57" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E57" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E57" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F57" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G57" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H57" s="21" t="str">
+        <v>18.299273358245291</v>
+      </c>
+      <c r="F57" s="21">
+        <f t="shared" si="5"/>
+        <v>81.700726641754713</v>
+      </c>
+      <c r="G57" s="21">
+        <f t="shared" si="4"/>
+        <v>5794.4085295122068</v>
+      </c>
+      <c r="H57" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>4205.5914704877932</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A58" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B58" s="23">
+        <f t="shared" si="3"/>
+        <v>57</v>
       </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="4" t="str">
+      <c r="D58" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E58" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E58" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F58" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G58" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H58" s="4" t="str">
+        <v>18.044842430362358</v>
+      </c>
+      <c r="F58" s="4">
+        <f t="shared" si="5"/>
+        <v>81.955157569637635</v>
+      </c>
+      <c r="G58" s="4">
+        <f t="shared" si="4"/>
+        <v>5712.453371942569</v>
+      </c>
+      <c r="H58" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>4287.546628057431</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="19"/>
-      <c r="B59" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A59" s="19">
+        <v>46238</v>
+      </c>
+      <c r="B59" s="24">
+        <f t="shared" si="3"/>
+        <v>58</v>
       </c>
       <c r="C59" s="20"/>
-      <c r="D59" s="21" t="str">
+      <c r="D59" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E59" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E59" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F59" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G59" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H59" s="21" t="str">
+        <v>17.789619158277308</v>
+      </c>
+      <c r="F59" s="21">
+        <f t="shared" si="5"/>
+        <v>82.210380841722696</v>
+      </c>
+      <c r="G59" s="21">
+        <f t="shared" si="4"/>
+        <v>5630.2429911008467</v>
+      </c>
+      <c r="H59" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>4369.7570088991533</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-      <c r="B60" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A60" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B60" s="23">
+        <f t="shared" si="3"/>
+        <v>59</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="4" t="str">
+      <c r="D60" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E60" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E60" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F60" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G60" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H60" s="4" t="str">
+        <v>17.533601074486132</v>
+      </c>
+      <c r="F60" s="4">
+        <f t="shared" si="5"/>
+        <v>82.466398925513872</v>
+      </c>
+      <c r="G60" s="4">
+        <f t="shared" si="4"/>
+        <v>5547.7765921753326</v>
+      </c>
+      <c r="H60" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>4452.2234078246674</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
-      <c r="B61" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A61" s="19">
+        <v>46240</v>
+      </c>
+      <c r="B61" s="24">
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="C61" s="20"/>
-      <c r="D61" s="21" t="str">
+      <c r="D61" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E61" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E61" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F61" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G61" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H61" s="21" t="str">
+        <v>17.276785703800563</v>
+      </c>
+      <c r="F61" s="21">
+        <f t="shared" si="5"/>
+        <v>82.723214296199444</v>
+      </c>
+      <c r="G61" s="21">
+        <f t="shared" si="4"/>
+        <v>5465.0533778791332</v>
+      </c>
+      <c r="H61" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>4534.9466221208668</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="2"/>
-      <c r="B62" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A62" s="2">
+        <v>46241</v>
+      </c>
+      <c r="B62" s="23">
+        <f t="shared" si="3"/>
+        <v>61</v>
       </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="4" t="str">
+      <c r="D62" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E62" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E62" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F62" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G62" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H62" s="4" t="str">
+        <v>17.019170563324149</v>
+      </c>
+      <c r="F62" s="4">
+        <f t="shared" si="5"/>
+        <v>82.980829436675847</v>
+      </c>
+      <c r="G62" s="4">
+        <f t="shared" si="4"/>
+        <v>5382.0725484424574</v>
+      </c>
+      <c r="H62" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>4617.9274515575426</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="4" r:id="rId1"/>
+    <sheet name="209" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -1146,7 +1147,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1184,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>5900</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1221,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>5382.0725484424574</v>
+        <v>4537.9176811721318</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1258,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4617.9274515575426</v>
+        <v>5462.0823188278682</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2687,283 +2688,303 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
-      <c r="B63" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A63" s="19">
+        <v>46242</v>
+      </c>
+      <c r="B63" s="24">
+        <f t="shared" si="3"/>
+        <v>62</v>
       </c>
       <c r="C63" s="20"/>
-      <c r="D63" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E63" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F63" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G63" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H63" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D63" s="21">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="E63" s="21">
+        <f t="shared" si="7"/>
+        <v>16.760753162428244</v>
+      </c>
+      <c r="F63" s="21">
+        <f t="shared" si="5"/>
+        <v>83.239246837571756</v>
+      </c>
+      <c r="G63" s="21">
+        <f t="shared" si="4"/>
+        <v>5298.8333016048855</v>
+      </c>
+      <c r="H63" s="21">
+        <f t="shared" si="8"/>
+        <v>4701.1666983951145</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A64" s="2">
+        <v>46243</v>
+      </c>
+      <c r="B64" s="23">
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="C64" s="3"/>
-      <c r="D64" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E64" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F64" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G64" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H64" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D64" s="4">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="E64" s="4">
+        <f t="shared" si="7"/>
+        <v>16.50153100272794</v>
+      </c>
+      <c r="F64" s="4">
+        <f t="shared" si="5"/>
+        <v>83.498468997272056</v>
+      </c>
+      <c r="G64" s="4">
+        <f t="shared" si="4"/>
+        <v>5215.3348326076139</v>
+      </c>
+      <c r="H64" s="4">
+        <f t="shared" si="8"/>
+        <v>4784.6651673923861</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="19"/>
-      <c r="B65" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A65" s="19">
+        <v>46244</v>
+      </c>
+      <c r="B65" s="24">
+        <f t="shared" si="3"/>
+        <v>64</v>
       </c>
       <c r="C65" s="20"/>
-      <c r="D65" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E65" s="21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F65" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G65" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H65" s="21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D65" s="21">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="E65" s="21">
+        <f t="shared" si="7"/>
+        <v>16.241501578057896</v>
+      </c>
+      <c r="F65" s="21">
+        <f t="shared" si="5"/>
+        <v>83.758498421942107</v>
+      </c>
+      <c r="G65" s="21">
+        <f t="shared" si="4"/>
+        <v>5131.5763341856718</v>
+      </c>
+      <c r="H65" s="21">
+        <f t="shared" si="8"/>
+        <v>4868.4236658143282</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="2"/>
-      <c r="B66" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A66" s="2">
+        <v>46245</v>
+      </c>
+      <c r="B66" s="23">
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="4" t="str">
+      <c r="D66" s="4">
         <f t="shared" ref="D66:D97" si="9">IF(AND($A66&lt;&gt;"",$B66&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E66" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F66" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G66" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H66" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <v>100</v>
+      </c>
+      <c r="E66" s="4">
+        <f t="shared" si="7"/>
+        <v>15.980662374448112</v>
+      </c>
+      <c r="F66" s="4">
+        <f t="shared" si="5"/>
+        <v>84.019337625551884</v>
+      </c>
+      <c r="G66" s="4">
+        <f t="shared" si="4"/>
+        <v>5047.5569965601198</v>
+      </c>
+      <c r="H66" s="4">
+        <f t="shared" si="8"/>
+        <v>4952.4430034398802</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="19"/>
-      <c r="B67" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A67" s="19">
+        <v>46246</v>
+      </c>
+      <c r="B67" s="24">
+        <f t="shared" si="3"/>
+        <v>66</v>
       </c>
       <c r="C67" s="20"/>
-      <c r="D67" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E67" s="21" t="str">
+      <c r="D67" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E67" s="21">
         <f t="shared" ref="E67:E98" si="10">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),G66*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F67" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G67" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H67" s="21" t="str">
+        <v>15.719010870099638</v>
+      </c>
+      <c r="F67" s="21">
+        <f t="shared" si="5"/>
+        <v>84.280989129900362</v>
+      </c>
+      <c r="G67" s="21">
+        <f t="shared" si="4"/>
+        <v>4963.2760074302196</v>
+      </c>
+      <c r="H67" s="21">
         <f t="shared" ref="H67:H98" si="11">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),$K$7-G67,"")</f>
-        <v/>
+        <v>5036.7239925697804</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="2"/>
-      <c r="B68" s="23" t="str">
+      <c r="A68" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B68" s="23">
         <f t="shared" ref="B68:B121" si="12">IF(A68&lt;&gt;"",B67+1,"")</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E68" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F68" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G68" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H68" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+      <c r="D68" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E68" s="4">
+        <f t="shared" si="10"/>
+        <v>15.456544535360178</v>
+      </c>
+      <c r="F68" s="4">
+        <f t="shared" si="5"/>
+        <v>84.54345546463982</v>
+      </c>
+      <c r="G68" s="4">
+        <f t="shared" si="4"/>
+        <v>4878.7325519655797</v>
+      </c>
+      <c r="H68" s="4">
+        <f t="shared" si="11"/>
+        <v>5121.2674480344203</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="19"/>
-      <c r="B69" s="24" t="str">
+      <c r="A69" s="19">
+        <v>46250</v>
+      </c>
+      <c r="B69" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>68</v>
       </c>
       <c r="C69" s="20"/>
-      <c r="D69" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E69" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F69" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G69" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H69" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+      <c r="D69" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E69" s="21">
+        <f t="shared" si="10"/>
+        <v>15.193260832699638</v>
+      </c>
+      <c r="F69" s="21">
+        <f t="shared" si="5"/>
+        <v>84.806739167300364</v>
+      </c>
+      <c r="G69" s="21">
+        <f t="shared" si="4"/>
+        <v>4793.9258127982794</v>
+      </c>
+      <c r="H69" s="21">
+        <f t="shared" si="11"/>
+        <v>5206.0741872017206</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="2"/>
-      <c r="B70" s="23" t="str">
+      <c r="A70" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B70" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>69</v>
       </c>
       <c r="C70" s="3"/>
-      <c r="D70" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E70" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F70" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G70" s="4" t="str">
+      <c r="D70" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E70" s="4">
+        <f t="shared" si="10"/>
+        <v>14.929157216685597</v>
+      </c>
+      <c r="F70" s="4">
+        <f t="shared" si="5"/>
+        <v>85.070842783314404</v>
+      </c>
+      <c r="G70" s="4">
         <f t="shared" ref="G70:G121" si="13">IF(AND($A70&lt;&gt;"",$B70&lt;&gt;""),G69-F70,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4708.8549700149651</v>
+      </c>
+      <c r="H70" s="4">
+        <f t="shared" si="11"/>
+        <v>5291.1450299850349</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="19"/>
-      <c r="B71" s="24" t="str">
+      <c r="A71" s="19">
+        <v>46254</v>
+      </c>
+      <c r="B71" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>70</v>
       </c>
       <c r="C71" s="20"/>
-      <c r="D71" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E71" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F71" s="21" t="str">
+      <c r="D71" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E71" s="21">
+        <f t="shared" si="10"/>
+        <v>14.664231133958694</v>
+      </c>
+      <c r="F71" s="21">
         <f t="shared" ref="F71:F121" si="14">IF(AND($A71&lt;&gt;"",$B71&lt;&gt;""),D71-E71,"")</f>
-        <v/>
-      </c>
-      <c r="G71" s="21" t="str">
+        <v>85.335768866041306</v>
+      </c>
+      <c r="G71" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H71" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4623.5192011489235</v>
+      </c>
+      <c r="H71" s="21">
+        <f t="shared" si="11"/>
+        <v>5376.4807988510765</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="2"/>
-      <c r="B72" s="23" t="str">
+      <c r="A72" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B72" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>71</v>
       </c>
       <c r="C72" s="3"/>
-      <c r="D72" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E72" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F72" s="4" t="str">
+      <c r="D72" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E72" s="4">
+        <f t="shared" si="10"/>
+        <v>14.398480023207934</v>
+      </c>
+      <c r="F72" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G72" s="4" t="str">
+        <v>85.601519976792062</v>
+      </c>
+      <c r="G72" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H72" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4537.9176811721318</v>
+      </c>
+      <c r="H72" s="4">
+        <f t="shared" si="11"/>
+        <v>5462.0823188278682</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -4342,4 +4363,3529 @@
   <sheetProtection algorithmName="SHA-512" hashValue="DDiEaF4cIciX4XA88UkRocQx7ujTBWEH9vcNnPtkt5AzvtATGftA/0UDdh6qxGa0FbbGF7EwED91zE01NtGHWQ==" saltValue="jwn+/pHeteXDQw6pCvBTNw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L121"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="1.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B2" s="23">
+        <f>IF(A2&lt;&gt;"",1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4">
+        <f t="shared" ref="D2:D65" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
+        <v>100</v>
+      </c>
+      <c r="E2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
+        <v>30.917065806268933</v>
+      </c>
+      <c r="F2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
+        <v>69.082934193731063</v>
+      </c>
+      <c r="G2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
+        <v>4930.9170658062685</v>
+      </c>
+      <c r="H2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
+        <v>69.082934193731489</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="26" t="str">
+        <f ca="1">IF(K3&lt;&gt;"",
+   "L" &amp; TEXT(K7,"0") &amp;
+   IF(J10="Weeks","W","D") &amp; K10 &amp;
+   "-" &amp; K3 &amp;
+   "-N" &amp; RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1))),
+   "")</f>
+        <v>L5000D60-Pratima-N209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="19">
+        <v>46248</v>
+      </c>
+      <c r="B3" s="24">
+        <f>IF(A3&lt;&gt;"",B2+1,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E3" s="21">
+        <f t="shared" ref="E3:E66" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
+        <v>30.489897481757385</v>
+      </c>
+      <c r="F3" s="21">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
+        <v>69.510102518242618</v>
+      </c>
+      <c r="G3" s="21">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
+        <v>4861.4069632880255</v>
+      </c>
+      <c r="H3" s="21">
+        <f t="shared" ref="H3:H66" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
+        <v>138.59303671197449</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B4" s="23">
+        <f t="shared" ref="B4:B67" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
+        <v>3</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="1"/>
+        <v>30.060087799005981</v>
+      </c>
+      <c r="F4" s="4">
+        <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
+        <v>69.939912200994016</v>
+      </c>
+      <c r="G4" s="4">
+        <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
+        <v>4791.4670510870319</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="2"/>
+        <v>208.5329489129681</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="27"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>46251</v>
+      </c>
+      <c r="B5" s="24">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>29.627620425405425</v>
+      </c>
+      <c r="F5" s="21">
+        <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),D5-E5,"")</f>
+        <v>70.372379574594575</v>
+      </c>
+      <c r="G5" s="21">
+        <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),G4-F5,"")</f>
+        <v>4721.0946715124373</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>278.90532848756266</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="27"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B6" s="23">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="1"/>
+        <v>29.192478927355129</v>
+      </c>
+      <c r="F6" s="4">
+        <f>IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),D6-E6,"")</f>
+        <v>70.807521072644874</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" ref="G6:G69" si="4">IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),G5-F6,"")</f>
+        <v>4650.2871504397926</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="2"/>
+        <v>349.71284956020736</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="27"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="19">
+        <v>46255</v>
+      </c>
+      <c r="B7" s="24">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>28.754646769638782</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" ref="F7:F70" si="5">IF(AND($A7&lt;&gt;"",$B7&lt;&gt;""),D7-E7,"")</f>
+        <v>71.245353230361218</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="4"/>
+        <v>4579.041797209431</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>420.95820279056898</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="28">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G8" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H8" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="29">
+        <f>RATE(K10,-K9,K7)</f>
+        <v>6.1834131612537868E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F9" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G9" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G10" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H10" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="31">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F11" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G11" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="L11" s="22"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G12" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H12" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="10">
+        <f>IFERROR(MAX($B:$B),"")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F13" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="12">
+        <f>(K10*K9)-K9*K12</f>
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G14" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H14" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="12">
+        <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
+        <v>4579.041797209431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19"/>
+      <c r="B15" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E15" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F15" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="14">
+        <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
+        <v>420.95820279056898</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G16" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H16" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="16">
+        <f>IF(A2,A2, "")</f>
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E17" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F17" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G17" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H17" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="18">
+        <f xml:space="preserve"> IF(A2,(K16 + 120),"")</f>
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G18" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E19" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F19" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G19" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H19" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G20" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H20" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E21" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F21" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G21" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H21" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F22" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G22" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H22" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="19"/>
+      <c r="B23" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E23" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F23" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G23" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H23" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F24" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G24" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="19"/>
+      <c r="B25" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E25" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F25" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G25" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H25" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="19"/>
+      <c r="B27" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E27" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F27" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G27" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H27" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G28" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="19"/>
+      <c r="B29" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E29" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F29" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G29" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H29" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G30" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H30" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="19"/>
+      <c r="B31" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E31" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F31" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G31" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H31" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G32" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H32" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="19"/>
+      <c r="B33" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E33" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F33" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G33" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H33" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E34" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F34" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G34" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H34" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="19"/>
+      <c r="B35" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E35" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F35" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G35" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H35" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F36" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G36" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H36" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="19"/>
+      <c r="B37" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E37" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F37" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G37" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H37" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F38" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G38" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H38" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="19"/>
+      <c r="B39" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E39" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F39" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G39" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H39" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E40" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F40" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G40" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H40" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="19"/>
+      <c r="B41" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E41" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F41" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G41" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H41" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F42" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G42" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H42" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="19"/>
+      <c r="B43" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C43" s="20"/>
+      <c r="D43" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E43" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F43" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G43" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H43" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F44" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G44" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H44" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="19"/>
+      <c r="B45" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E45" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F45" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G45" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H45" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F46" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G46" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H46" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="19"/>
+      <c r="B47" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E47" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F47" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G47" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H47" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F48" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G48" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H48" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="19"/>
+      <c r="B49" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C49" s="20"/>
+      <c r="D49" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E49" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F49" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G49" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H49" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F50" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G50" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H50" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="19"/>
+      <c r="B51" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E51" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F51" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G51" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H51" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F52" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G52" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H52" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="19"/>
+      <c r="B53" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C53" s="20"/>
+      <c r="D53" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E53" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F53" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G53" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H53" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+      <c r="B54" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E54" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F54" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G54" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H54" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="19"/>
+      <c r="B55" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C55" s="20"/>
+      <c r="D55" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E55" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F55" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G55" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H55" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2"/>
+      <c r="B56" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F56" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G56" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H56" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="19"/>
+      <c r="B57" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C57" s="20"/>
+      <c r="D57" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E57" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F57" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G57" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H57" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E58" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F58" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G58" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H58" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="19"/>
+      <c r="B59" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E59" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F59" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G59" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H59" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="2"/>
+      <c r="B60" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E60" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F60" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G60" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H60" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="19"/>
+      <c r="B61" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C61" s="20"/>
+      <c r="D61" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E61" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F61" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G61" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H61" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="2"/>
+      <c r="B62" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E62" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F62" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G62" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H62" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="19"/>
+      <c r="B63" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C63" s="20"/>
+      <c r="D63" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E63" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F63" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G63" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H63" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="2"/>
+      <c r="B64" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E64" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F64" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G64" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H64" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="19"/>
+      <c r="B65" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C65" s="20"/>
+      <c r="D65" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E65" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F65" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G65" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H65" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="2"/>
+      <c r="B66" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="4" t="str">
+        <f t="shared" ref="D66:D121" si="6">IF(AND($A66&lt;&gt;"",$B66&lt;&gt;""),$K$9,"")</f>
+        <v/>
+      </c>
+      <c r="E66" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F66" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G66" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H66" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="19"/>
+      <c r="B67" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C67" s="20"/>
+      <c r="D67" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E67" s="21" t="str">
+        <f t="shared" ref="E67:E121" si="7">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),G66*$K$8,"")</f>
+        <v/>
+      </c>
+      <c r="F67" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G67" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H67" s="21" t="str">
+        <f t="shared" ref="H67:H121" si="8">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),$K$7-G67,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="2"/>
+      <c r="B68" s="23" t="str">
+        <f t="shared" ref="B68:B121" si="9">IF(A68&lt;&gt;"",B67+1,"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E68" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F68" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G68" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H68" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="19"/>
+      <c r="B69" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C69" s="20"/>
+      <c r="D69" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E69" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F69" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G69" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H69" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="2"/>
+      <c r="B70" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E70" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F70" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G70" s="4" t="str">
+        <f t="shared" ref="G70:G121" si="10">IF(AND($A70&lt;&gt;"",$B70&lt;&gt;""),G69-F70,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="19"/>
+      <c r="B71" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C71" s="20"/>
+      <c r="D71" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E71" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F71" s="21" t="str">
+        <f t="shared" ref="F71:F121" si="11">IF(AND($A71&lt;&gt;"",$B71&lt;&gt;""),D71-E71,"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H71" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="2"/>
+      <c r="B72" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E72" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F72" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G72" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H72" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="19"/>
+      <c r="B73" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C73" s="20"/>
+      <c r="D73" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E73" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F73" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G73" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H73" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="2"/>
+      <c r="B74" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E74" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F74" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G74" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H74" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="19"/>
+      <c r="B75" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C75" s="20"/>
+      <c r="D75" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E75" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F75" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G75" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H75" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2"/>
+      <c r="B76" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E76" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F76" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G76" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H76" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="19"/>
+      <c r="B77" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C77" s="20"/>
+      <c r="D77" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E77" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F77" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G77" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H77" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="2"/>
+      <c r="B78" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E78" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F78" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G78" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H78" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="19"/>
+      <c r="B79" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C79" s="20"/>
+      <c r="D79" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E79" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F79" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G79" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H79" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="2"/>
+      <c r="B80" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E80" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F80" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G80" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H80" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="19"/>
+      <c r="B81" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C81" s="20"/>
+      <c r="D81" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E81" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F81" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G81" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H81" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2"/>
+      <c r="B82" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E82" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F82" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G82" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H82" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="19"/>
+      <c r="B83" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C83" s="20"/>
+      <c r="D83" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E83" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F83" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G83" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H83" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2"/>
+      <c r="B84" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E84" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F84" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G84" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H84" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="19"/>
+      <c r="B85" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C85" s="20"/>
+      <c r="D85" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E85" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F85" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G85" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H85" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="2"/>
+      <c r="B86" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E86" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F86" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G86" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H86" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="19"/>
+      <c r="B87" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C87" s="20"/>
+      <c r="D87" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E87" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F87" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G87" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H87" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="2"/>
+      <c r="B88" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E88" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F88" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G88" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H88" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="19"/>
+      <c r="B89" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C89" s="20"/>
+      <c r="D89" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E89" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F89" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G89" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H89" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="2"/>
+      <c r="B90" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E90" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F90" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G90" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H90" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="19"/>
+      <c r="B91" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C91" s="20"/>
+      <c r="D91" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E91" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F91" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G91" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H91" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2"/>
+      <c r="B92" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E92" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F92" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G92" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H92" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="19"/>
+      <c r="B93" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C93" s="20"/>
+      <c r="D93" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E93" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F93" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G93" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H93" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="2"/>
+      <c r="B94" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E94" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F94" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G94" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H94" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="19"/>
+      <c r="B95" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C95" s="20"/>
+      <c r="D95" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E95" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F95" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G95" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H95" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="2"/>
+      <c r="B96" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E96" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F96" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G96" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H96" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="19"/>
+      <c r="B97" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C97" s="20"/>
+      <c r="D97" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E97" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F97" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G97" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H97" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="2"/>
+      <c r="B98" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E98" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F98" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G98" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H98" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="19"/>
+      <c r="B99" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C99" s="20"/>
+      <c r="D99" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E99" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F99" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G99" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H99" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="2"/>
+      <c r="B100" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E100" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F100" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G100" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H100" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="19"/>
+      <c r="B101" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C101" s="20"/>
+      <c r="D101" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E101" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F101" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G101" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H101" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="2"/>
+      <c r="B102" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E102" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F102" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G102" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H102" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="19"/>
+      <c r="B103" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C103" s="20"/>
+      <c r="D103" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E103" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F103" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G103" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H103" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="2"/>
+      <c r="B104" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E104" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F104" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G104" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H104" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="19"/>
+      <c r="B105" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E105" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F105" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G105" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H105" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="2"/>
+      <c r="B106" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E106" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F106" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G106" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H106" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="19"/>
+      <c r="B107" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C107" s="20"/>
+      <c r="D107" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E107" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F107" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G107" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H107" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="2"/>
+      <c r="B108" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E108" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F108" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G108" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H108" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="19"/>
+      <c r="B109" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E109" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F109" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G109" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H109" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="2"/>
+      <c r="B110" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E110" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F110" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G110" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H110" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="19"/>
+      <c r="B111" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C111" s="20"/>
+      <c r="D111" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E111" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F111" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G111" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H111" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="2"/>
+      <c r="B112" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E112" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F112" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G112" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H112" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="19"/>
+      <c r="B113" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C113" s="20"/>
+      <c r="D113" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E113" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F113" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G113" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H113" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="2"/>
+      <c r="B114" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E114" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F114" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G114" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H114" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="19"/>
+      <c r="B115" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C115" s="20"/>
+      <c r="D115" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E115" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F115" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G115" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H115" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="2"/>
+      <c r="B116" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E116" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F116" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G116" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H116" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="19"/>
+      <c r="B117" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C117" s="20"/>
+      <c r="D117" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E117" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F117" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G117" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H117" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="2"/>
+      <c r="B118" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E118" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F118" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G118" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H118" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="19"/>
+      <c r="B119" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C119" s="20"/>
+      <c r="D119" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E119" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F119" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G119" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H119" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="2"/>
+      <c r="B120" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E120" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F120" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G120" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H120" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="19"/>
+      <c r="B121" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C121" s="20"/>
+      <c r="D121" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E121" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F121" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G121" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H121" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/NBFC-MF/Borrowers/Pratima_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Pratima_Daily.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="4" r:id="rId1"/>
     <sheet name="209" sheetId="5" r:id="rId2"/>
+    <sheet name="221" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -1147,7 +1148,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>71</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1184,7 +1185,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>4900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1221,7 +1222,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>4537.9176811721318</v>
+        <v>4.5272940951690543E-10</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1258,7 +1259,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>5462.0823188278682</v>
+        <v>9999.9999999995471</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2988,1375 +2989,1473 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="19"/>
-      <c r="B73" s="24" t="str">
+      <c r="A73" s="19">
+        <v>46256</v>
+      </c>
+      <c r="B73" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>72</v>
       </c>
       <c r="C73" s="20"/>
-      <c r="D73" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E73" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F73" s="21" t="str">
+      <c r="D73" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E73" s="21">
+        <f t="shared" si="10"/>
+        <v>14.131901315145946</v>
+      </c>
+      <c r="F73" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G73" s="21" t="str">
+        <v>85.868098684854061</v>
+      </c>
+      <c r="G73" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H73" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4452.0495824872778</v>
+      </c>
+      <c r="H73" s="21">
+        <f t="shared" si="11"/>
+        <v>5547.9504175127222</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="2"/>
-      <c r="B74" s="23" t="str">
+      <c r="A74" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B74" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>73</v>
       </c>
       <c r="C74" s="3"/>
-      <c r="D74" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E74" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F74" s="4" t="str">
+      <c r="D74" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E74" s="4">
+        <f t="shared" si="10"/>
+        <v>13.864492432484123</v>
+      </c>
+      <c r="F74" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G74" s="4" t="str">
+        <v>86.135507567515873</v>
+      </c>
+      <c r="G74" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H74" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4365.9140749197622</v>
+      </c>
+      <c r="H74" s="4">
+        <f t="shared" si="11"/>
+        <v>5634.0859250802378</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="19"/>
-      <c r="B75" s="24" t="str">
+      <c r="A75" s="19">
+        <v>46258</v>
+      </c>
+      <c r="B75" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>74</v>
       </c>
       <c r="C75" s="20"/>
-      <c r="D75" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E75" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F75" s="21" t="str">
+      <c r="D75" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E75" s="21">
+        <f t="shared" si="10"/>
+        <v>13.596250789907716</v>
+      </c>
+      <c r="F75" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G75" s="21" t="str">
+        <v>86.403749210092286</v>
+      </c>
+      <c r="G75" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H75" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4279.5103257096698</v>
+      </c>
+      <c r="H75" s="21">
+        <f t="shared" si="11"/>
+        <v>5720.4896742903302</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="2"/>
-      <c r="B76" s="23" t="str">
+      <c r="A76" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B76" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>75</v>
       </c>
       <c r="C76" s="3"/>
-      <c r="D76" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E76" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F76" s="4" t="str">
+      <c r="D76" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E76" s="4">
+        <f t="shared" si="10"/>
+        <v>13.327173794050829</v>
+      </c>
+      <c r="F76" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G76" s="4" t="str">
+        <v>86.672826205949178</v>
+      </c>
+      <c r="G76" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H76" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4192.8374995037202</v>
+      </c>
+      <c r="H76" s="4">
+        <f t="shared" si="11"/>
+        <v>5807.1625004962798</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="19"/>
-      <c r="B77" s="24" t="str">
+      <c r="A77" s="19">
+        <v>46260</v>
+      </c>
+      <c r="B77" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>76</v>
       </c>
       <c r="C77" s="20"/>
-      <c r="D77" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E77" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F77" s="21" t="str">
+      <c r="D77" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E77" s="21">
+        <f t="shared" si="10"/>
+        <v>13.057258843471359</v>
+      </c>
+      <c r="F77" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G77" s="21" t="str">
+        <v>86.942741156528641</v>
+      </c>
+      <c r="G77" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H77" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4105.8947583471918</v>
+      </c>
+      <c r="H77" s="21">
+        <f t="shared" si="11"/>
+        <v>5894.1052416528082</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="2"/>
-      <c r="B78" s="23" t="str">
+      <c r="A78" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B78" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>77</v>
       </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E78" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F78" s="4" t="str">
+      <c r="D78" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E78" s="4">
+        <f t="shared" si="10"/>
+        <v>12.786503328625843</v>
+      </c>
+      <c r="F78" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G78" s="4" t="str">
+        <v>87.213496671374159</v>
+      </c>
+      <c r="G78" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H78" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>4018.6812616758175</v>
+      </c>
+      <c r="H78" s="4">
+        <f t="shared" si="11"/>
+        <v>5981.318738324182</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="19"/>
-      <c r="B79" s="24" t="str">
+      <c r="A79" s="19">
+        <v>46262</v>
+      </c>
+      <c r="B79" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>78</v>
       </c>
       <c r="C79" s="20"/>
-      <c r="D79" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E79" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F79" s="21" t="str">
+      <c r="D79" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E79" s="21">
+        <f t="shared" si="10"/>
+        <v>12.514904631844212</v>
+      </c>
+      <c r="F79" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G79" s="21" t="str">
+        <v>87.485095368155783</v>
+      </c>
+      <c r="G79" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H79" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3931.1961663076618</v>
+      </c>
+      <c r="H79" s="21">
+        <f t="shared" si="11"/>
+        <v>6068.8038336923382</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="2"/>
-      <c r="B80" s="23" t="str">
+      <c r="A80" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B80" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>79</v>
       </c>
       <c r="C80" s="3"/>
-      <c r="D80" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E80" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F80" s="4" t="str">
+      <c r="D80" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E80" s="4">
+        <f t="shared" si="10"/>
+        <v>12.242460127304506</v>
+      </c>
+      <c r="F80" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G80" s="4" t="str">
+        <v>87.757539872695489</v>
+      </c>
+      <c r="G80" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H80" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3843.4386264349664</v>
+      </c>
+      <c r="H80" s="4">
+        <f t="shared" si="11"/>
+        <v>6156.5613735650331</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="19"/>
-      <c r="B81" s="24" t="str">
+      <c r="A81" s="19">
+        <v>46264</v>
+      </c>
+      <c r="B81" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>80</v>
       </c>
       <c r="C81" s="20"/>
-      <c r="D81" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E81" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F81" s="21" t="str">
+      <c r="D81" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E81" s="21">
+        <f t="shared" si="10"/>
+        <v>11.969167181007478</v>
+      </c>
+      <c r="F81" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G81" s="21" t="str">
+        <v>88.030832818992522</v>
+      </c>
+      <c r="G81" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H81" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3755.4077936159738</v>
+      </c>
+      <c r="H81" s="21">
+        <f t="shared" si="11"/>
+        <v>6244.5922063840262</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="2"/>
-      <c r="B82" s="23" t="str">
+      <c r="A82" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B82" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>81</v>
       </c>
       <c r="C82" s="3"/>
-      <c r="D82" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E82" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F82" s="4" t="str">
+      <c r="D82" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E82" s="4">
+        <f t="shared" si="10"/>
+        <v>11.695023150751119</v>
+      </c>
+      <c r="F82" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G82" s="4" t="str">
+        <v>88.304976849248874</v>
+      </c>
+      <c r="G82" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H82" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3667.102816766725</v>
+      </c>
+      <c r="H82" s="4">
+        <f t="shared" si="11"/>
+        <v>6332.8971832332754</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="19"/>
-      <c r="B83" s="24" t="str">
+      <c r="A83" s="19">
+        <v>46267</v>
+      </c>
+      <c r="B83" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>82</v>
       </c>
       <c r="C83" s="20"/>
-      <c r="D83" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E83" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F83" s="21" t="str">
+      <c r="D83" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E83" s="21">
+        <f t="shared" si="10"/>
+        <v>11.420025386105134</v>
+      </c>
+      <c r="F83" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G83" s="21" t="str">
+        <v>88.579974613894862</v>
+      </c>
+      <c r="G83" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H83" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3578.52284215283</v>
+      </c>
+      <c r="H83" s="21">
+        <f t="shared" si="11"/>
+        <v>6421.47715784717</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="2"/>
-      <c r="B84" s="23" t="str">
+      <c r="A84" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B84" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>83</v>
       </c>
       <c r="C84" s="3"/>
-      <c r="D84" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E84" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F84" s="4" t="str">
+      <c r="D84" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E84" s="4">
+        <f t="shared" si="10"/>
+        <v>11.144171228385297</v>
+      </c>
+      <c r="F84" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G84" s="4" t="str">
+        <v>88.855828771614711</v>
+      </c>
+      <c r="G84" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H84" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3489.6670133812154</v>
+      </c>
+      <c r="H84" s="4">
+        <f t="shared" si="11"/>
+        <v>6510.3329866187851</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="19"/>
-      <c r="B85" s="24" t="str">
+      <c r="A85" s="19">
+        <v>46269</v>
+      </c>
+      <c r="B85" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>84</v>
       </c>
       <c r="C85" s="20"/>
-      <c r="D85" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E85" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F85" s="21" t="str">
+      <c r="D85" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E85" s="21">
+        <f t="shared" si="10"/>
+        <v>10.867458010627759</v>
+      </c>
+      <c r="F85" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G85" s="21" t="str">
+        <v>89.132541989372243</v>
+      </c>
+      <c r="G85" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H85" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3400.534471391843</v>
+      </c>
+      <c r="H85" s="21">
+        <f t="shared" si="11"/>
+        <v>6599.465528608157</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="2"/>
-      <c r="B86" s="23" t="str">
+      <c r="A86" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B86" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>85</v>
       </c>
       <c r="C86" s="3"/>
-      <c r="D86" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E86" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F86" s="4" t="str">
+      <c r="D86" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E86" s="4">
+        <f t="shared" si="10"/>
+        <v>10.589883057563259</v>
+      </c>
+      <c r="F86" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G86" s="4" t="str">
+        <v>89.410116942436744</v>
+      </c>
+      <c r="G86" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H86" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3311.1243544494064</v>
+      </c>
+      <c r="H86" s="4">
+        <f t="shared" si="11"/>
+        <v>6688.8756455505936</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="19"/>
-      <c r="B87" s="24" t="str">
+      <c r="A87" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B87" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>86</v>
       </c>
       <c r="C87" s="20"/>
-      <c r="D87" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E87" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F87" s="21" t="str">
+      <c r="D87" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E87" s="21">
+        <f t="shared" si="10"/>
+        <v>10.311443685591266</v>
+      </c>
+      <c r="F87" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G87" s="21" t="str">
+        <v>89.688556314408729</v>
+      </c>
+      <c r="G87" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H87" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3221.4357981349976</v>
+      </c>
+      <c r="H87" s="21">
+        <f t="shared" si="11"/>
+        <v>6778.5642018650024</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="2"/>
-      <c r="B88" s="23" t="str">
+      <c r="A88" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B88" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>87</v>
       </c>
       <c r="C88" s="3"/>
-      <c r="D88" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E88" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F88" s="4" t="str">
+      <c r="D88" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E88" s="4">
+        <f t="shared" si="10"/>
+        <v>10.032137202754022</v>
+      </c>
+      <c r="F88" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G88" s="4" t="str">
+        <v>89.967862797245971</v>
+      </c>
+      <c r="G88" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H88" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3131.4679353377514</v>
+      </c>
+      <c r="H88" s="4">
+        <f t="shared" si="11"/>
+        <v>6868.5320646622486</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="19"/>
-      <c r="B89" s="24" t="str">
+      <c r="A89" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B89" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>88</v>
       </c>
       <c r="C89" s="20"/>
-      <c r="D89" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E89" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F89" s="21" t="str">
+      <c r="D89" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E89" s="21">
+        <f t="shared" si="10"/>
+        <v>9.7519609087105223</v>
+      </c>
+      <c r="F89" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G89" s="21" t="str">
+        <v>90.248039091289485</v>
+      </c>
+      <c r="G89" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H89" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>3041.2198962464618</v>
+      </c>
+      <c r="H89" s="21">
+        <f t="shared" si="11"/>
+        <v>6958.7801037535382</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="2"/>
-      <c r="B90" s="23" t="str">
+      <c r="A90" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B90" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>89</v>
       </c>
       <c r="C90" s="3"/>
-      <c r="D90" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E90" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F90" s="4" t="str">
+      <c r="D90" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E90" s="4">
+        <f t="shared" si="10"/>
+        <v>9.4709120947104175</v>
+      </c>
+      <c r="F90" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G90" s="4" t="str">
+        <v>90.529087905289586</v>
+      </c>
+      <c r="G90" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H90" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2950.6908083411722</v>
+      </c>
+      <c r="H90" s="4">
+        <f t="shared" si="11"/>
+        <v>7049.3091916588273</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="19"/>
-      <c r="B91" s="24" t="str">
+      <c r="A91" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B91" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>90</v>
       </c>
       <c r="C91" s="20"/>
-      <c r="D91" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E91" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F91" s="21" t="str">
+      <c r="D91" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E91" s="21">
+        <f t="shared" si="10"/>
+        <v>9.1889880435678073</v>
+      </c>
+      <c r="F91" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G91" s="21" t="str">
+        <v>90.811011956432196</v>
+      </c>
+      <c r="G91" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H91" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2859.8797963847401</v>
+      </c>
+      <c r="H91" s="21">
+        <f t="shared" si="11"/>
+        <v>7140.1202036152599</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="2"/>
-      <c r="B92" s="23" t="str">
+      <c r="A92" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B92" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>91</v>
       </c>
       <c r="C92" s="3"/>
-      <c r="D92" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E92" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F92" s="4" t="str">
+      <c r="D92" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E92" s="4">
+        <f t="shared" si="10"/>
+        <v>8.906186029634986</v>
+      </c>
+      <c r="F92" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G92" s="4" t="str">
+        <v>91.093813970365019</v>
+      </c>
+      <c r="G92" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H92" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2768.7859824143752</v>
+      </c>
+      <c r="H92" s="4">
+        <f t="shared" si="11"/>
+        <v>7231.2140175856248</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="19"/>
-      <c r="B93" s="24" t="str">
+      <c r="A93" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B93" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>92</v>
       </c>
       <c r="C93" s="20"/>
-      <c r="D93" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E93" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F93" s="21" t="str">
+      <c r="D93" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E93" s="21">
+        <f t="shared" si="10"/>
+        <v>8.6225033187760829</v>
+      </c>
+      <c r="F93" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G93" s="21" t="str">
+        <v>91.377496681223917</v>
+      </c>
+      <c r="G93" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H93" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2677.4084857331513</v>
+      </c>
+      <c r="H93" s="21">
+        <f t="shared" si="11"/>
+        <v>7322.5915142668491</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="2"/>
-      <c r="B94" s="23" t="str">
+      <c r="A94" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B94" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>93</v>
       </c>
       <c r="C94" s="3"/>
-      <c r="D94" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E94" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F94" s="4" t="str">
+      <c r="D94" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E94" s="4">
+        <f t="shared" si="10"/>
+        <v>8.3379371683406287</v>
+      </c>
+      <c r="F94" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G94" s="4" t="str">
+        <v>91.66206283165937</v>
+      </c>
+      <c r="G94" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H94" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2585.7464229014918</v>
+      </c>
+      <c r="H94" s="4">
+        <f t="shared" si="11"/>
+        <v>7414.2535770985087</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="19"/>
-      <c r="B95" s="24" t="str">
+      <c r="A95" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B95" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>94</v>
       </c>
       <c r="C95" s="20"/>
-      <c r="D95" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E95" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F95" s="21" t="str">
+      <c r="D95" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E95" s="21">
+        <f t="shared" si="10"/>
+        <v>8.0524848271370466</v>
+      </c>
+      <c r="F95" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G95" s="21" t="str">
+        <v>91.94751517286295</v>
+      </c>
+      <c r="G95" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H95" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2493.7989077286288</v>
+      </c>
+      <c r="H95" s="21">
+        <f t="shared" si="11"/>
+        <v>7506.2010922713707</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="2"/>
-      <c r="B96" s="23" t="str">
+      <c r="A96" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B96" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>95</v>
       </c>
       <c r="C96" s="3"/>
-      <c r="D96" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E96" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F96" s="4" t="str">
+      <c r="D96" s="4">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E96" s="4">
+        <f t="shared" si="10"/>
+        <v>7.7661435354060435</v>
+      </c>
+      <c r="F96" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G96" s="4" t="str">
+        <v>92.233856464593956</v>
+      </c>
+      <c r="G96" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H96" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2401.565051264035</v>
+      </c>
+      <c r="H96" s="4">
+        <f t="shared" si="11"/>
+        <v>7598.434948735965</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="19"/>
-      <c r="B97" s="24" t="str">
+      <c r="A97" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B97" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>96</v>
       </c>
       <c r="C97" s="20"/>
-      <c r="D97" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E97" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F97" s="21" t="str">
+      <c r="D97" s="21">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="E97" s="21">
+        <f t="shared" si="10"/>
+        <v>7.478910524793938</v>
+      </c>
+      <c r="F97" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G97" s="21" t="str">
+        <v>92.521089475206068</v>
+      </c>
+      <c r="G97" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H97" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2309.0439617888287</v>
+      </c>
+      <c r="H97" s="21">
+        <f t="shared" si="11"/>
+        <v>7690.9560382111713</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="2"/>
-      <c r="B98" s="23" t="str">
+      <c r="A98" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B98" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>97</v>
       </c>
       <c r="C98" s="3"/>
-      <c r="D98" s="4" t="str">
+      <c r="D98" s="4">
         <f t="shared" ref="D98:D121" si="15">IF(AND($A98&lt;&gt;"",$B98&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E98" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F98" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E98" s="4">
+        <f t="shared" si="10"/>
+        <v>7.1907830183258881</v>
+      </c>
+      <c r="F98" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G98" s="4" t="str">
+        <v>92.809216981674112</v>
+      </c>
+      <c r="G98" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H98" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+        <v>2216.2347448071546</v>
+      </c>
+      <c r="H98" s="4">
+        <f t="shared" si="11"/>
+        <v>7783.7652551928459</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="19"/>
-      <c r="B99" s="24" t="str">
+      <c r="A99" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B99" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>98</v>
       </c>
       <c r="C99" s="20"/>
-      <c r="D99" s="21" t="str">
+      <c r="D99" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E99" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E99" s="21">
         <f t="shared" ref="E99:E121" si="16">IF(AND($A99&lt;&gt;"",$B99&lt;&gt;""),G98*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F99" s="21" t="str">
+        <v>6.9017582303790492</v>
+      </c>
+      <c r="F99" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G99" s="21" t="str">
+        <v>93.098241769620955</v>
+      </c>
+      <c r="G99" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H99" s="21" t="str">
+        <v>2123.1365030375337</v>
+      </c>
+      <c r="H99" s="21">
         <f t="shared" ref="H99:H121" si="17">IF(AND($A99&lt;&gt;"",$B99&lt;&gt;""),$K$7-G99,"")</f>
-        <v/>
+        <v>7876.8634969624663</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="2"/>
-      <c r="B100" s="23" t="str">
+      <c r="A100" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B100" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>99</v>
       </c>
       <c r="C100" s="3"/>
-      <c r="D100" s="4" t="str">
+      <c r="D100" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E100" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E100" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F100" s="4" t="str">
+        <v>6.611833366655639</v>
+      </c>
+      <c r="F100" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G100" s="4" t="str">
+        <v>93.388166633344355</v>
+      </c>
+      <c r="G100" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H100" s="4" t="str">
+        <v>2029.7483364041893</v>
+      </c>
+      <c r="H100" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>7970.2516635958109</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="19"/>
-      <c r="B101" s="24" t="str">
+      <c r="A101" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B101" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>100</v>
       </c>
       <c r="C101" s="20"/>
-      <c r="D101" s="21" t="str">
+      <c r="D101" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E101" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E101" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F101" s="21" t="str">
+        <v>6.3210056241559256</v>
+      </c>
+      <c r="F101" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G101" s="21" t="str">
+        <v>93.67899437584407</v>
+      </c>
+      <c r="G101" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H101" s="21" t="str">
+        <v>1936.0693420283453</v>
+      </c>
+      <c r="H101" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8063.9306579716549</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="2"/>
-      <c r="B102" s="23" t="str">
+      <c r="A102" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B102" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>101</v>
       </c>
       <c r="C102" s="3"/>
-      <c r="D102" s="4" t="str">
+      <c r="D102" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E102" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E102" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F102" s="4" t="str">
+        <v>6.0292721911511231</v>
+      </c>
+      <c r="F102" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G102" s="4" t="str">
+        <v>93.970727808848878</v>
+      </c>
+      <c r="G102" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H102" s="4" t="str">
+        <v>1842.0986142194965</v>
+      </c>
+      <c r="H102" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8157.9013857805039</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="19"/>
-      <c r="B103" s="24" t="str">
+      <c r="A103" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B103" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>102</v>
       </c>
       <c r="C103" s="20"/>
-      <c r="D103" s="21" t="str">
+      <c r="D103" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E103" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E103" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F103" s="21" t="str">
+        <v>5.7366302471562118</v>
+      </c>
+      <c r="F103" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G103" s="21" t="str">
+        <v>94.263369752843786</v>
+      </c>
+      <c r="G103" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H103" s="21" t="str">
+        <v>1747.8352444666527</v>
+      </c>
+      <c r="H103" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8252.1647555333475</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="2"/>
-      <c r="B104" s="23" t="str">
+      <c r="A104" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B104" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>103</v>
       </c>
       <c r="C104" s="3"/>
-      <c r="D104" s="4" t="str">
+      <c r="D104" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E104" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E104" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F104" s="4" t="str">
+        <v>5.4430769629026683</v>
+      </c>
+      <c r="F104" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G104" s="4" t="str">
+        <v>94.556923037097334</v>
+      </c>
+      <c r="G104" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H104" s="4" t="str">
+        <v>1653.2783214295555</v>
+      </c>
+      <c r="H104" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8346.7216785704441</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="19"/>
-      <c r="B105" s="24" t="str">
+      <c r="A105" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B105" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>104</v>
       </c>
       <c r="C105" s="20"/>
-      <c r="D105" s="21" t="str">
+      <c r="D105" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E105" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E105" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F105" s="21" t="str">
+        <v>5.1486095003111139</v>
+      </c>
+      <c r="F105" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G105" s="21" t="str">
+        <v>94.85139049968889</v>
+      </c>
+      <c r="G105" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H105" s="21" t="str">
+        <v>1558.4269309298666</v>
+      </c>
+      <c r="H105" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8441.573069070133</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="2"/>
-      <c r="B106" s="23" t="str">
+      <c r="A106" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B106" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>105</v>
       </c>
       <c r="C106" s="3"/>
-      <c r="D106" s="4" t="str">
+      <c r="D106" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E106" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E106" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F106" s="4" t="str">
+        <v>4.8532250124638718</v>
+      </c>
+      <c r="F106" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G106" s="4" t="str">
+        <v>95.146774987536133</v>
+      </c>
+      <c r="G106" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H106" s="4" t="str">
+        <v>1463.2801559423303</v>
+      </c>
+      <c r="H106" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8536.7198440576703</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="19"/>
-      <c r="B107" s="24" t="str">
+      <c r="A107" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B107" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>106</v>
       </c>
       <c r="C107" s="20"/>
-      <c r="D107" s="21" t="str">
+      <c r="D107" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E107" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E107" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F107" s="21" t="str">
+        <v>4.5569206435774463</v>
+      </c>
+      <c r="F107" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G107" s="21" t="str">
+        <v>95.443079356422558</v>
+      </c>
+      <c r="G107" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H107" s="21" t="str">
+        <v>1367.8370765859079</v>
+      </c>
+      <c r="H107" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8632.1629234140928</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="2"/>
-      <c r="B108" s="23" t="str">
+      <c r="A108" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B108" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>107</v>
       </c>
       <c r="C108" s="3"/>
-      <c r="D108" s="4" t="str">
+      <c r="D108" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E108" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E108" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F108" s="4" t="str">
+        <v>4.259693528974914</v>
+      </c>
+      <c r="F108" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G108" s="4" t="str">
+        <v>95.740306471025093</v>
+      </c>
+      <c r="G108" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H108" s="4" t="str">
+        <v>1272.0967701148827</v>
+      </c>
+      <c r="H108" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8727.903229885118</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="19"/>
-      <c r="B109" s="24" t="str">
+      <c r="A109" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B109" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>108</v>
       </c>
       <c r="C109" s="20"/>
-      <c r="D109" s="21" t="str">
+      <c r="D109" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E109" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E109" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F109" s="21" t="str">
+        <v>3.9615407950582244</v>
+      </c>
+      <c r="F109" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G109" s="21" t="str">
+        <v>96.038459204941773</v>
+      </c>
+      <c r="G109" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H109" s="21" t="str">
+        <v>1176.0583109099409</v>
+      </c>
+      <c r="H109" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8823.9416890900593</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="2"/>
-      <c r="B110" s="23" t="str">
+      <c r="A110" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B110" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>109</v>
       </c>
       <c r="C110" s="3"/>
-      <c r="D110" s="4" t="str">
+      <c r="D110" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E110" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E110" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F110" s="4" t="str">
+        <v>3.6624595592804208</v>
+      </c>
+      <c r="F110" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G110" s="4" t="str">
+        <v>96.337540440719579</v>
+      </c>
+      <c r="G110" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H110" s="4" t="str">
+        <v>1079.7207704692214</v>
+      </c>
+      <c r="H110" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>8920.279229530779</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="19"/>
-      <c r="B111" s="24" t="str">
+      <c r="A111" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B111" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>110</v>
       </c>
       <c r="C111" s="20"/>
-      <c r="D111" s="21" t="str">
+      <c r="D111" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E111" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E111" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F111" s="21" t="str">
+        <v>3.3624469301177702</v>
+      </c>
+      <c r="F111" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G111" s="21" t="str">
+        <v>96.63755306988223</v>
+      </c>
+      <c r="G111" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H111" s="21" t="str">
+        <v>983.08321739933922</v>
+      </c>
+      <c r="H111" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9016.9167826006615</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="2"/>
-      <c r="B112" s="23" t="str">
+      <c r="A112" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B112" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>111</v>
       </c>
       <c r="C112" s="3"/>
-      <c r="D112" s="4" t="str">
+      <c r="D112" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E112" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E112" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F112" s="4" t="str">
+        <v>3.061500007041809</v>
+      </c>
+      <c r="F112" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G112" s="4" t="str">
+        <v>96.938499992958185</v>
+      </c>
+      <c r="G112" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H112" s="4" t="str">
+        <v>886.14471740638101</v>
+      </c>
+      <c r="H112" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9113.8552825936185</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="19"/>
-      <c r="B113" s="24" t="str">
+      <c r="A113" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B113" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>112</v>
       </c>
       <c r="C113" s="20"/>
-      <c r="D113" s="21" t="str">
+      <c r="D113" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E113" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E113" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F113" s="21" t="str">
+        <v>2.7596158804912996</v>
+      </c>
+      <c r="F113" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G113" s="21" t="str">
+        <v>97.240384119508704</v>
+      </c>
+      <c r="G113" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H113" s="21" t="str">
+        <v>788.90433328687232</v>
+      </c>
+      <c r="H113" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9211.0956667131286</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="2"/>
-      <c r="B114" s="23" t="str">
+      <c r="A114" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B114" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>113</v>
       </c>
       <c r="C114" s="3"/>
-      <c r="D114" s="4" t="str">
+      <c r="D114" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E114" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E114" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F114" s="4" t="str">
+        <v>2.4567916318441023</v>
+      </c>
+      <c r="F114" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G114" s="4" t="str">
+        <v>97.543208368155902</v>
+      </c>
+      <c r="G114" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H114" s="4" t="str">
+        <v>691.36112491871643</v>
+      </c>
+      <c r="H114" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9308.6388750812839</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="19"/>
-      <c r="B115" s="24" t="str">
+      <c r="A115" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B115" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>114</v>
       </c>
       <c r="C115" s="20"/>
-      <c r="D115" s="21" t="str">
+      <c r="D115" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E115" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E115" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F115" s="21" t="str">
+        <v>2.1530243333889567</v>
+      </c>
+      <c r="F115" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G115" s="21" t="str">
+        <v>97.846975666611044</v>
+      </c>
+      <c r="G115" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H115" s="21" t="str">
+        <v>593.51414925210543</v>
+      </c>
+      <c r="H115" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9406.4858507478948</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="2"/>
-      <c r="B116" s="23" t="str">
+      <c r="A116" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B116" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>115</v>
       </c>
       <c r="C116" s="3"/>
-      <c r="D116" s="4" t="str">
+      <c r="D116" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E116" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E116" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F116" s="4" t="str">
+        <v>1.8483110482971767</v>
+      </c>
+      <c r="F116" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G116" s="4" t="str">
+        <v>98.151688951702823</v>
+      </c>
+      <c r="G116" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H116" s="4" t="str">
+        <v>495.36246030040263</v>
+      </c>
+      <c r="H116" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9504.6375396995973</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="19"/>
-      <c r="B117" s="24" t="str">
+      <c r="A117" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B117" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>116</v>
       </c>
       <c r="C117" s="20"/>
-      <c r="D117" s="21" t="str">
+      <c r="D117" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E117" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E117" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F117" s="21" t="str">
+        <v>1.5426488305942569</v>
+      </c>
+      <c r="F117" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G117" s="21" t="str">
+        <v>98.45735116940574</v>
+      </c>
+      <c r="G117" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H117" s="21" t="str">
+        <v>396.90510913099689</v>
+      </c>
+      <c r="H117" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9603.0948908690025</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="2"/>
-      <c r="B118" s="23" t="str">
+      <c r="A118" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B118" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>117</v>
       </c>
       <c r="C118" s="3"/>
-      <c r="D118" s="4" t="str">
+      <c r="D118" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E118" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E118" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F118" s="4" t="str">
+        <v>1.2360347251313921</v>
+      </c>
+      <c r="F118" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G118" s="4" t="str">
+        <v>98.76396527486861</v>
+      </c>
+      <c r="G118" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H118" s="4" t="str">
+        <v>298.14114385612828</v>
+      </c>
+      <c r="H118" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9701.8588561438719</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="19"/>
-      <c r="B119" s="24" t="str">
+      <c r="A119" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B119" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>118</v>
       </c>
       <c r="C119" s="20"/>
-      <c r="D119" s="21" t="str">
+      <c r="D119" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E119" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E119" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F119" s="21" t="str">
+        <v>0.92846576755690546</v>
+      </c>
+      <c r="F119" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G119" s="21" t="str">
+        <v>99.071534232443099</v>
+      </c>
+      <c r="G119" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H119" s="21" t="str">
+        <v>199.06960962368518</v>
+      </c>
+      <c r="H119" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9800.9303903763157</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="2"/>
-      <c r="B120" s="23" t="str">
+      <c r="A120" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B120" s="23">
         <f t="shared" si="12"/>
-        <v/>
+        <v>119</v>
       </c>
       <c r="C120" s="3"/>
-      <c r="D120" s="4" t="str">
+      <c r="D120" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E120" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E120" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F120" s="4" t="str">
+        <v>0.61993898428758998</v>
+      </c>
+      <c r="F120" s="4">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G120" s="4" t="str">
+        <v>99.380061015712414</v>
+      </c>
+      <c r="G120" s="4">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H120" s="4" t="str">
+        <v>99.689548607972768</v>
+      </c>
+      <c r="H120" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9900.310451392028</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="19"/>
-      <c r="B121" s="24" t="str">
+      <c r="A121" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B121" s="24">
         <f t="shared" si="12"/>
-        <v/>
+        <v>120</v>
       </c>
       <c r="C121" s="20"/>
-      <c r="D121" s="21" t="str">
+      <c r="D121" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E121" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E121" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F121" s="21" t="str">
+        <v>0.31045139247995929</v>
+      </c>
+      <c r="F121" s="21">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G121" s="21" t="str">
+        <v>99.689548607520038</v>
+      </c>
+      <c r="G121" s="21">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H121" s="21" t="str">
+        <v>4.5272940951690543E-10</v>
+      </c>
+      <c r="H121" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>9999.9999999995471</v>
       </c>
     </row>
   </sheetData>
@@ -4629,31 +4728,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B8" s="23">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="1"/>
+        <v>28.31410731479599</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="5"/>
+        <v>71.68589268520401</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="4"/>
+        <v>4507.3559045242273</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="2"/>
+        <v>492.6440954757727</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>14</v>
@@ -4664,31 +4765,33 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46257</v>
+      </c>
+      <c r="B9" s="24">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>27.870843822490073</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="5"/>
+        <v>72.129156177509927</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="4"/>
+        <v>4435.2267483467176</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>564.77325165328239</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>8</v>
@@ -4698,31 +4801,33 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B10" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="1"/>
+        <v>27.424839448871932</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="5"/>
+        <v>72.575160551128064</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="4"/>
+        <v>4362.6515877955899</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="2"/>
+        <v>637.34841220441012</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>15</v>
@@ -4732,201 +4837,213 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46259</v>
+      </c>
+      <c r="B11" s="24">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>26.97607724593998</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="5"/>
+        <v>73.023922754060024</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="4"/>
+        <v>4289.6276650415302</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>710.37233495846976</v>
       </c>
       <c r="J11" s="8"/>
       <c r="L11" s="22"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B12" s="23">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D12" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="1"/>
+        <v>26.524540160896148</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="5"/>
+        <v>73.475459839103848</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="4"/>
+        <v>4216.1522052024266</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="2"/>
+        <v>783.84779479757344</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46261</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>26.070211035497859</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>73.929788964502137</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>4142.2224162379243</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>857.77758376207566</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>5400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="1"/>
+        <v>25.613072605406042</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>74.386927394593954</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>4067.8354888433305</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="2"/>
+        <v>932.1645111566695</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>4579.041797209431</v>
+        <v>-3.4034997042908799E-11</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46263</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>25.153107499529082</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>74.846892500470915</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>3992.9885963428596</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>1007.0114036571404</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>420.95820279056898</v>
+        <v>5000.0000000000337</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46264</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="1"/>
+        <v>24.690298239362722</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>75.309701760637282</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>3917.6788945822223</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="2"/>
+        <v>1082.3211054177777</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -4937,31 +5054,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46265</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>24.224627238325901</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>75.775372761674106</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>3841.9035218205481</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>1158.0964781794519</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -4972,1237 +5091,1325 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D18" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="1"/>
+        <v>23.756076801092451</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>76.243923198907552</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>3765.6595986216407</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>1234.3404013783593</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46268</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D19" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E19" s="21">
+        <f t="shared" si="1"/>
+        <v>23.284629122918705</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>76.715370877081298</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>3688.9442277445596</v>
+      </c>
+      <c r="H19" s="21">
+        <f t="shared" si="2"/>
+        <v>1311.0557722554404</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D20" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="1"/>
+        <v>22.810266288966897</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>77.189733711033099</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>3611.7544940335265</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="2"/>
+        <v>1388.2455059664735</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46270</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D21" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E21" s="21">
+        <f t="shared" si="1"/>
+        <v>22.332970273624419</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>77.667029726375574</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>3534.0874643071511</v>
+      </c>
+      <c r="H21" s="21">
+        <f t="shared" si="2"/>
+        <v>1465.9125356928489</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D22" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="1"/>
+        <v>21.852722939818861</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>78.147277060181139</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>3455.9401872469698</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="2"/>
+        <v>1544.0598127530302</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A23" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B23" s="24">
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H23" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D23" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E23" s="21">
+        <f t="shared" si="1"/>
+        <v>21.36950603832879</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="5"/>
+        <v>78.630493961671206</v>
+      </c>
+      <c r="G23" s="21">
+        <f t="shared" si="4"/>
+        <v>3377.3096932852986</v>
+      </c>
+      <c r="H23" s="21">
+        <f t="shared" si="2"/>
+        <v>1622.6903067147014</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A24" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B24" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D24" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="1"/>
+        <v>20.883301207090305</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="5"/>
+        <v>79.116698792909688</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="4"/>
+        <v>3298.1929944923891</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="2"/>
+        <v>1701.8070055076109</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A25" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B25" s="24">
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H25" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D25" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E25" s="21">
+        <f t="shared" si="1"/>
+        <v>20.394089970499277</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="5"/>
+        <v>79.60591002950072</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="4"/>
+        <v>3218.5870844628885</v>
+      </c>
+      <c r="H25" s="21">
+        <f t="shared" si="2"/>
+        <v>1781.4129155371115</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A26" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="23">
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E26" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D26" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="1"/>
+        <v>19.901853738709278</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="5"/>
+        <v>80.098146261290722</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="4"/>
+        <v>3138.4889382015976</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="2"/>
+        <v>1861.5110617984024</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A27" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="24">
+        <f t="shared" si="3"/>
+        <v>26</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G27" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D27" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E27" s="21">
+        <f t="shared" si="1"/>
+        <v>19.406573806925181</v>
+      </c>
+      <c r="F27" s="21">
+        <f t="shared" si="5"/>
+        <v>80.593426193074819</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="4"/>
+        <v>3057.8955120085229</v>
+      </c>
+      <c r="H27" s="21">
+        <f t="shared" si="2"/>
+        <v>1942.1044879914771</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A28" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B28" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D28" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="1"/>
+        <v>18.908231354692386</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="5"/>
+        <v>81.09176864530761</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="4"/>
+        <v>2976.8037433632153</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" si="2"/>
+        <v>2023.1962566367847</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A29" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H29" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D29" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E29" s="21">
+        <f t="shared" si="1"/>
+        <v>18.406807445181645</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>81.593192554818359</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="4"/>
+        <v>2895.2105508083969</v>
+      </c>
+      <c r="H29" s="21">
+        <f t="shared" si="2"/>
+        <v>2104.7894491916031</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A30" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B30" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D30" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="1"/>
+        <v>17.902283024469465</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="5"/>
+        <v>82.097716975530531</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>2813.1128338328663</v>
+      </c>
+      <c r="H30" s="4">
+        <f t="shared" si="2"/>
+        <v>2186.8871661671337</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A31" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="C31" s="20"/>
-      <c r="D31" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E31" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H31" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D31" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E31" s="21">
+        <f t="shared" si="1"/>
+        <v>17.394638920814081</v>
+      </c>
+      <c r="F31" s="21">
+        <f t="shared" si="5"/>
+        <v>82.605361079185911</v>
+      </c>
+      <c r="G31" s="21">
+        <f t="shared" si="4"/>
+        <v>2730.5074727536803</v>
+      </c>
+      <c r="H31" s="21">
+        <f t="shared" si="2"/>
+        <v>2269.4925272463197</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A32" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B32" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E32" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D32" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="1"/>
+        <v>16.883855843926924</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="5"/>
+        <v>83.116144156073076</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="4"/>
+        <v>2647.3913285976073</v>
+      </c>
+      <c r="H32" s="4">
+        <f t="shared" si="2"/>
+        <v>2352.6086714023927</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A33" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="C33" s="20"/>
-      <c r="D33" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E33" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H33" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D33" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E33" s="21">
+        <f t="shared" si="1"/>
+        <v>16.369914384239593</v>
+      </c>
+      <c r="F33" s="21">
+        <f t="shared" si="5"/>
+        <v>83.630085615760407</v>
+      </c>
+      <c r="G33" s="21">
+        <f t="shared" si="4"/>
+        <v>2563.7612429818469</v>
+      </c>
+      <c r="H33" s="21">
+        <f t="shared" si="2"/>
+        <v>2436.2387570181531</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A34" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B34" s="23">
+        <f t="shared" si="3"/>
+        <v>33</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E34" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F34" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D34" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="1"/>
+        <v>15.85279501216632</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="5"/>
+        <v>84.147204987833675</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="4"/>
+        <v>2479.6140379940134</v>
+      </c>
+      <c r="H34" s="4">
+        <f t="shared" si="2"/>
+        <v>2520.3859620059866</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A35" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B35" s="24">
+        <f t="shared" si="3"/>
+        <v>34</v>
       </c>
       <c r="C35" s="20"/>
-      <c r="D35" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E35" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F35" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H35" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D35" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E35" s="21">
+        <f t="shared" si="1"/>
+        <v>15.332478077361831</v>
+      </c>
+      <c r="F35" s="21">
+        <f t="shared" si="5"/>
+        <v>84.667521922638173</v>
+      </c>
+      <c r="G35" s="21">
+        <f t="shared" si="4"/>
+        <v>2394.9465160713753</v>
+      </c>
+      <c r="H35" s="21">
+        <f t="shared" si="2"/>
+        <v>2605.0534839286247</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A36" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B36" s="23">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E36" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F36" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G36" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H36" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D36" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="1"/>
+        <v>14.808943807974646</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="5"/>
+        <v>85.191056192025357</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="4"/>
+        <v>2309.7554598793499</v>
+      </c>
+      <c r="H36" s="4">
+        <f t="shared" si="2"/>
+        <v>2690.2445401206501</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
-      <c r="B37" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A37" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B37" s="24">
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
       <c r="C37" s="20"/>
-      <c r="D37" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E37" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F37" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G37" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H37" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D37" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E37" s="21">
+        <f t="shared" si="1"/>
+        <v>14.282172309895765</v>
+      </c>
+      <c r="F37" s="21">
+        <f t="shared" si="5"/>
+        <v>85.71782769010423</v>
+      </c>
+      <c r="G37" s="21">
+        <f t="shared" si="4"/>
+        <v>2224.0376321892459</v>
+      </c>
+      <c r="H37" s="21">
+        <f t="shared" si="2"/>
+        <v>2775.9623678107541</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A38" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B38" s="23">
+        <f t="shared" si="3"/>
+        <v>37</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E38" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F38" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G38" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H38" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D38" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="1"/>
+        <v>13.752143566002692</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="5"/>
+        <v>86.247856433997313</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="4"/>
+        <v>2137.7897757552487</v>
+      </c>
+      <c r="H38" s="4">
+        <f t="shared" si="2"/>
+        <v>2862.2102242447513</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A39" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B39" s="24">
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="C39" s="20"/>
-      <c r="D39" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E39" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F39" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G39" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H39" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D39" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E39" s="21">
+        <f t="shared" si="1"/>
+        <v>13.218837435398786</v>
+      </c>
+      <c r="F39" s="21">
+        <f t="shared" si="5"/>
+        <v>86.781162564601217</v>
+      </c>
+      <c r="G39" s="21">
+        <f t="shared" si="4"/>
+        <v>2051.0086131906473</v>
+      </c>
+      <c r="H39" s="21">
+        <f t="shared" si="2"/>
+        <v>2948.9913868093527</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B40" s="23">
+        <f t="shared" si="3"/>
+        <v>39</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E40" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F40" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G40" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H40" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D40" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="1"/>
+        <v>12.682233652647925</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="5"/>
+        <v>87.317766347352077</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="4"/>
+        <v>1963.6908468432953</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" si="2"/>
+        <v>3036.3091531567047</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A41" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B41" s="24">
+        <f t="shared" si="3"/>
+        <v>40</v>
       </c>
       <c r="C41" s="20"/>
-      <c r="D41" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E41" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F41" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G41" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H41" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D41" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E41" s="21">
+        <f t="shared" si="1"/>
+        <v>12.142311827004427</v>
+      </c>
+      <c r="F41" s="21">
+        <f t="shared" si="5"/>
+        <v>87.85768817299558</v>
+      </c>
+      <c r="G41" s="21">
+        <f t="shared" si="4"/>
+        <v>1875.8331586702998</v>
+      </c>
+      <c r="H41" s="21">
+        <f t="shared" si="2"/>
+        <v>3124.1668413297002</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A42" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B42" s="23">
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E42" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F42" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H42" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D42" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E42" s="4">
+        <f t="shared" si="1"/>
+        <v>11.599051441638194</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="5"/>
+        <v>88.400948558361804</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="4"/>
+        <v>1787.432210111938</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="2"/>
+        <v>3212.5677898880622</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A43" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B43" s="24">
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
       <c r="C43" s="20"/>
-      <c r="D43" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E43" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F43" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G43" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H43" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D43" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E43" s="21">
+        <f t="shared" si="1"/>
+        <v>11.052431852855102</v>
+      </c>
+      <c r="F43" s="21">
+        <f t="shared" si="5"/>
+        <v>88.947568147144892</v>
+      </c>
+      <c r="G43" s="21">
+        <f t="shared" si="4"/>
+        <v>1698.4846419647931</v>
+      </c>
+      <c r="H43" s="21">
+        <f t="shared" si="2"/>
+        <v>3301.5153580352071</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A44" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B44" s="23">
+        <f t="shared" si="3"/>
+        <v>43</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E44" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F44" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G44" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H44" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D44" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E44" s="4">
+        <f t="shared" si="1"/>
+        <v>10.502432289312528</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" si="5"/>
+        <v>89.497567710687477</v>
+      </c>
+      <c r="G44" s="4">
+        <f t="shared" si="4"/>
+        <v>1608.9870742541057</v>
+      </c>
+      <c r="H44" s="4">
+        <f t="shared" si="2"/>
+        <v>3391.0129257458943</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A45" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B45" s="24">
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="C45" s="20"/>
-      <c r="D45" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E45" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F45" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G45" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H45" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D45" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E45" s="21">
+        <f t="shared" si="1"/>
+        <v>9.9490318512300604</v>
+      </c>
+      <c r="F45" s="21">
+        <f t="shared" si="5"/>
+        <v>90.05096814876994</v>
+      </c>
+      <c r="G45" s="21">
+        <f t="shared" si="4"/>
+        <v>1518.9361061053357</v>
+      </c>
+      <c r="H45" s="21">
+        <f t="shared" si="2"/>
+        <v>3481.063893894664</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A46" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B46" s="23">
+        <f t="shared" si="3"/>
+        <v>45</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E46" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F46" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G46" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H46" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D46" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E46" s="4">
+        <f t="shared" si="1"/>
+        <v>9.3922095095953111</v>
+      </c>
+      <c r="F46" s="4">
+        <f t="shared" si="5"/>
+        <v>90.607790490404682</v>
+      </c>
+      <c r="G46" s="4">
+        <f t="shared" si="4"/>
+        <v>1428.3283156149309</v>
+      </c>
+      <c r="H46" s="4">
+        <f t="shared" si="2"/>
+        <v>3571.6716843850691</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
-      <c r="B47" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A47" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B47" s="24">
+        <f t="shared" si="3"/>
+        <v>46</v>
       </c>
       <c r="C47" s="20"/>
-      <c r="D47" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E47" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F47" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G47" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H47" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D47" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E47" s="21">
+        <f t="shared" si="1"/>
+        <v>8.8319441053648173</v>
+      </c>
+      <c r="F47" s="21">
+        <f t="shared" si="5"/>
+        <v>91.168055894635188</v>
+      </c>
+      <c r="G47" s="21">
+        <f t="shared" si="4"/>
+        <v>1337.1602597202957</v>
+      </c>
+      <c r="H47" s="21">
+        <f t="shared" si="2"/>
+        <v>3662.8397402797045</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A48" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B48" s="23">
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E48" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F48" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G48" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H48" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D48" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="1"/>
+        <v>8.2682143486600079</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="5"/>
+        <v>91.73178565133999</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="4"/>
+        <v>1245.4284740689557</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="2"/>
+        <v>3754.5715259310446</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
-      <c r="B49" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A49" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B49" s="24">
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="C49" s="20"/>
-      <c r="D49" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E49" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F49" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G49" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H49" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D49" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E49" s="21">
+        <f t="shared" si="1"/>
+        <v>7.700998817958201</v>
+      </c>
+      <c r="F49" s="21">
+        <f t="shared" si="5"/>
+        <v>92.299001182041792</v>
+      </c>
+      <c r="G49" s="21">
+        <f t="shared" si="4"/>
+        <v>1153.1294728869138</v>
+      </c>
+      <c r="H49" s="21">
+        <f t="shared" si="2"/>
+        <v>3846.8705271130862</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A50" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B50" s="23">
+        <f t="shared" si="3"/>
+        <v>49</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E50" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F50" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G50" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H50" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D50" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" si="1"/>
+        <v>7.1302759592785847</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" si="5"/>
+        <v>92.869724040721422</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="4"/>
+        <v>1060.2597488461925</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="2"/>
+        <v>3939.7402511538075</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A51" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B51" s="24">
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="C51" s="20"/>
-      <c r="D51" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E51" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F51" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G51" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H51" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D51" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E51" s="21">
+        <f t="shared" si="1"/>
+        <v>6.5560240853631813</v>
+      </c>
+      <c r="F51" s="21">
+        <f t="shared" si="5"/>
+        <v>93.443975914636823</v>
+      </c>
+      <c r="G51" s="21">
+        <f t="shared" si="4"/>
+        <v>966.81577293155567</v>
+      </c>
+      <c r="H51" s="21">
+        <f t="shared" si="2"/>
+        <v>4033.1842270684442</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A52" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B52" s="23">
+        <f t="shared" si="3"/>
+        <v>51</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E52" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F52" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G52" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H52" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D52" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" si="1"/>
+        <v>5.9782213748527342</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="5"/>
+        <v>94.021778625147263</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="4"/>
+        <v>872.79399430640842</v>
+      </c>
+      <c r="H52" s="4">
+        <f t="shared" si="2"/>
+        <v>4127.2060056935916</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
-      <c r="B53" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A53" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B53" s="24">
+        <f t="shared" si="3"/>
+        <v>52</v>
       </c>
       <c r="C53" s="20"/>
-      <c r="D53" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E53" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F53" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G53" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H53" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D53" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E53" s="21">
+        <f t="shared" si="1"/>
+        <v>5.3968458714575087</v>
+      </c>
+      <c r="F53" s="21">
+        <f t="shared" si="5"/>
+        <v>94.603154128542485</v>
+      </c>
+      <c r="G53" s="21">
+        <f t="shared" si="4"/>
+        <v>778.19084017786599</v>
+      </c>
+      <c r="H53" s="21">
+        <f t="shared" si="2"/>
+        <v>4221.8091598221345</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="2"/>
-      <c r="B54" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A54" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B54" s="23">
+        <f t="shared" si="3"/>
+        <v>53</v>
       </c>
       <c r="C54" s="3"/>
-      <c r="D54" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E54" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F54" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G54" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H54" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D54" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E54" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8118754831229591</v>
+      </c>
+      <c r="F54" s="4">
+        <f t="shared" si="5"/>
+        <v>95.188124516877039</v>
+      </c>
+      <c r="G54" s="4">
+        <f t="shared" si="4"/>
+        <v>683.002715660989</v>
+      </c>
+      <c r="H54" s="4">
+        <f t="shared" si="2"/>
+        <v>4316.9972843390115</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="19"/>
-      <c r="B55" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A55" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B55" s="24">
+        <f t="shared" si="3"/>
+        <v>54</v>
       </c>
       <c r="C55" s="20"/>
-      <c r="D55" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E55" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F55" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G55" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H55" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D55" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E55" s="21">
+        <f t="shared" si="1"/>
+        <v>4.2232879811902375</v>
+      </c>
+      <c r="F55" s="21">
+        <f t="shared" si="5"/>
+        <v>95.776712018809761</v>
+      </c>
+      <c r="G55" s="21">
+        <f t="shared" si="4"/>
+        <v>587.22600364217919</v>
+      </c>
+      <c r="H55" s="21">
+        <f t="shared" si="2"/>
+        <v>4412.7739963578206</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A56" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B56" s="23">
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E56" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F56" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G56" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H56" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D56" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E56" s="4">
+        <f t="shared" si="1"/>
+        <v>3.6310609995515151</v>
+      </c>
+      <c r="F56" s="4">
+        <f t="shared" si="5"/>
+        <v>96.368939000448478</v>
+      </c>
+      <c r="G56" s="4">
+        <f t="shared" si="4"/>
+        <v>490.85706464173074</v>
+      </c>
+      <c r="H56" s="4">
+        <f t="shared" si="2"/>
+        <v>4509.1429353582689</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
-      <c r="B57" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A57" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B57" s="24">
+        <f t="shared" si="3"/>
+        <v>56</v>
       </c>
       <c r="C57" s="20"/>
-      <c r="D57" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E57" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F57" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G57" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H57" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D57" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E57" s="21">
+        <f t="shared" si="1"/>
+        <v>3.0351720338000785</v>
+      </c>
+      <c r="F57" s="21">
+        <f t="shared" si="5"/>
+        <v>96.96482796619992</v>
+      </c>
+      <c r="G57" s="21">
+        <f t="shared" si="4"/>
+        <v>393.89223667553085</v>
+      </c>
+      <c r="H57" s="21">
+        <f t="shared" si="2"/>
+        <v>4606.1077633244695</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A58" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B58" s="23">
+        <f t="shared" si="3"/>
+        <v>57</v>
       </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E58" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F58" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G58" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H58" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D58" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E58" s="4">
+        <f t="shared" si="1"/>
+        <v>2.4355984403751689</v>
+      </c>
+      <c r="F58" s="4">
+        <f t="shared" si="5"/>
+        <v>97.564401559624827</v>
+      </c>
+      <c r="G58" s="4">
+        <f t="shared" si="4"/>
+        <v>296.32783511590605</v>
+      </c>
+      <c r="H58" s="4">
+        <f t="shared" si="2"/>
+        <v>4703.6721648840939</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="19"/>
-      <c r="B59" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A59" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B59" s="24">
+        <f t="shared" si="3"/>
+        <v>58</v>
       </c>
       <c r="C59" s="20"/>
-      <c r="D59" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E59" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F59" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G59" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H59" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D59" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E59" s="21">
+        <f t="shared" si="1"/>
+        <v>1.8323174357015355</v>
+      </c>
+      <c r="F59" s="21">
+        <f t="shared" si="5"/>
+        <v>98.16768256429846</v>
+      </c>
+      <c r="G59" s="21">
+        <f t="shared" si="4"/>
+        <v>198.16015255160761</v>
+      </c>
+      <c r="H59" s="21">
+        <f t="shared" si="2"/>
+        <v>4801.839847448392</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-      <c r="B60" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A60" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B60" s="23">
+        <f t="shared" si="3"/>
+        <v>59</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E60" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F60" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G60" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H60" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D60" s="4">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E60" s="4">
+        <f t="shared" si="1"/>
+        <v>1.2253060953236687</v>
+      </c>
+      <c r="F60" s="4">
+        <f t="shared" si="5"/>
+        <v>98.774693904676326</v>
+      </c>
+      <c r="G60" s="4">
+        <f t="shared" si="4"/>
+        <v>99.385458646931284</v>
+      </c>
+      <c r="H60" s="4">
+        <f t="shared" si="2"/>
+        <v>4900.6145413530685</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
-      <c r="B61" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A61" s="19">
+        <v>46272</v>
+      </c>
+      <c r="B61" s="24">
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="C61" s="20"/>
-      <c r="D61" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E61" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F61" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G61" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H61" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D61" s="21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E61" s="21">
+        <f t="shared" si="1"/>
+        <v>0.61454135303467883</v>
+      </c>
+      <c r="F61" s="21">
+        <f t="shared" si="5"/>
+        <v>99.385458646965319</v>
+      </c>
+      <c r="G61" s="21">
+        <f t="shared" si="4"/>
+        <v>-3.4034997042908799E-11</v>
+      </c>
+      <c r="H61" s="21">
+        <f t="shared" si="2"/>
+        <v>5000.0000000000337</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
@@ -7888,4 +8095,3525 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L121"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="1.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B2" s="23">
+        <f>IF(A2&lt;&gt;"",1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4">
+        <f t="shared" ref="D2:D65" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
+        <v>200</v>
+      </c>
+      <c r="E2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
+        <v>62.283638920024281</v>
+      </c>
+      <c r="F2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
+        <v>137.71636107997571</v>
+      </c>
+      <c r="G2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
+        <v>19862.283638920024</v>
+      </c>
+      <c r="H2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
+        <v>137.7163610799762</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="26" t="str">
+        <f ca="1">IF(K3&lt;&gt;"",
+   "L" &amp; TEXT(K7,"0") &amp;
+   IF(J10="Weeks","W","D") &amp; K10 &amp;
+   "-" &amp; K3 &amp;
+   "-N" &amp; RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1))),
+   "")</f>
+        <v>L20000D120-Pratima-N221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="19">
+        <v>46274</v>
+      </c>
+      <c r="B3" s="24">
+        <f>IF(A3&lt;&gt;"",B2+1,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E3" s="21">
+        <f t="shared" ref="E3:E66" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
+        <v>61.854765114680035</v>
+      </c>
+      <c r="F3" s="21">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
+        <v>138.14523488531995</v>
+      </c>
+      <c r="G3" s="21">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
+        <v>19724.138404034704</v>
+      </c>
+      <c r="H3" s="21">
+        <f t="shared" ref="H3:H66" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
+        <v>275.86159596529615</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B4" s="23">
+        <f t="shared" ref="B4:B67" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
+        <v>3</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="1"/>
+        <v>61.424555718274078</v>
+      </c>
+      <c r="F4" s="4">
+        <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
+        <v>138.57544428172594</v>
+      </c>
+      <c r="G4" s="4">
+        <f>IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
+        <v>19585.562959752977</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="2"/>
+        <v>414.43704024702311</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="27"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>46276</v>
+      </c>
+      <c r="B5" s="24">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>60.993006571532824</v>
+      </c>
+      <c r="F5" s="21">
+        <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),D5-E5,"")</f>
+        <v>139.00699342846718</v>
+      </c>
+      <c r="G5" s="21">
+        <f>IF(AND($A5&lt;&gt;"",$B5&lt;&gt;""),G4-F5,"")</f>
+        <v>19446.555966324511</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>553.44403367548875</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="27"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="str">
+        <f>IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),D6-E6,"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="4" t="str">
+        <f t="shared" ref="G6:G69" si="4">IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),G5-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="27"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="19"/>
+      <c r="B7" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F7" s="21" t="str">
+        <f t="shared" ref="F7:F70" si="5">IF(AND($A7&lt;&gt;"",$B7&lt;&gt;""),D7-E7,"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H7" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="28">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G8" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H8" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="29">
+        <f>RATE(K10,-K9,K7)</f>
+        <v>3.1141819460012141E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F9" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G9" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="30">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G10" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H10" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="31">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F11" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G11" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="L11" s="22"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G12" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H12" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="10">
+        <f>IFERROR(MAX($B:$B),"")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F13" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="12">
+        <f>(K10*K9)-K9*K12</f>
+        <v>23200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G14" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H14" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="12">
+        <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
+        <v>19446.555966324511</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19"/>
+      <c r="B15" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E15" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F15" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="14">
+        <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
+        <v>553.44403367548875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G16" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H16" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="16">
+        <f>IF(A2,A2, "")</f>
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E17" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F17" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G17" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H17" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="18">
+        <f xml:space="preserve"> IF(A2,(K16 + 120),"")</f>
+        <v>46393</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G18" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E19" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F19" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G19" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H19" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F20" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G20" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H20" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E21" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F21" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G21" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H21" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F22" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G22" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H22" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="19"/>
+      <c r="B23" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E23" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F23" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G23" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H23" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F24" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G24" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="19"/>
+      <c r="B25" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E25" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F25" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G25" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H25" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F26" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="19"/>
+      <c r="B27" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E27" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F27" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G27" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H27" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F28" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G28" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="19"/>
+      <c r="B29" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E29" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F29" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G29" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H29" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F30" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G30" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H30" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="19"/>
+      <c r="B31" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E31" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F31" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G31" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H31" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F32" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G32" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H32" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="19"/>
+      <c r="B33" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E33" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F33" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G33" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H33" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E34" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F34" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G34" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H34" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="19"/>
+      <c r="B35" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E35" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F35" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G35" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H35" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F36" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G36" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H36" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="19"/>
+      <c r="B37" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E37" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F37" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G37" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H37" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F38" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G38" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H38" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="19"/>
+      <c r="B39" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E39" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F39" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G39" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H39" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E40" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F40" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G40" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H40" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="19"/>
+      <c r="B41" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E41" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F41" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G41" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H41" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F42" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G42" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H42" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="19"/>
+      <c r="B43" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C43" s="20"/>
+      <c r="D43" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E43" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F43" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G43" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H43" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F44" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G44" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H44" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="19"/>
+      <c r="B45" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E45" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F45" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G45" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H45" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F46" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G46" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H46" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="19"/>
+      <c r="B47" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E47" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F47" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G47" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H47" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F48" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G48" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H48" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="19"/>
+      <c r="B49" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C49" s="20"/>
+      <c r="D49" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E49" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F49" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G49" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H49" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F50" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G50" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H50" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="19"/>
+      <c r="B51" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E51" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F51" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G51" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H51" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F52" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G52" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H52" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="19"/>
+      <c r="B53" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C53" s="20"/>
+      <c r="D53" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E53" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F53" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G53" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H53" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+      <c r="B54" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E54" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F54" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G54" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H54" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="19"/>
+      <c r="B55" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C55" s="20"/>
+      <c r="D55" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E55" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F55" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G55" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H55" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2"/>
+      <c r="B56" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F56" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G56" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H56" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="19"/>
+      <c r="B57" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C57" s="20"/>
+      <c r="D57" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E57" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F57" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G57" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H57" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E58" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F58" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G58" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H58" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="19"/>
+      <c r="B59" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E59" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F59" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G59" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H59" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="2"/>
+      <c r="B60" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E60" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F60" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G60" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H60" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="19"/>
+      <c r="B61" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C61" s="20"/>
+      <c r="D61" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E61" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F61" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G61" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H61" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="2"/>
+      <c r="B62" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E62" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F62" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G62" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H62" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="19"/>
+      <c r="B63" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C63" s="20"/>
+      <c r="D63" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E63" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F63" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G63" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H63" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="2"/>
+      <c r="B64" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E64" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F64" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G64" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H64" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="19"/>
+      <c r="B65" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C65" s="20"/>
+      <c r="D65" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E65" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F65" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G65" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H65" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="2"/>
+      <c r="B66" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="4" t="str">
+        <f t="shared" ref="D66:D121" si="6">IF(AND($A66&lt;&gt;"",$B66&lt;&gt;""),$K$9,"")</f>
+        <v/>
+      </c>
+      <c r="E66" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F66" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G66" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H66" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="19"/>
+      <c r="B67" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C67" s="20"/>
+      <c r="D67" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E67" s="21" t="str">
+        <f t="shared" ref="E67:E121" si="7">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),G66*$K$8,"")</f>
+        <v/>
+      </c>
+      <c r="F67" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G67" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H67" s="21" t="str">
+        <f t="shared" ref="H67:H121" si="8">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),$K$7-G67,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="2"/>
+      <c r="B68" s="23" t="str">
+        <f t="shared" ref="B68:B121" si="9">IF(A68&lt;&gt;"",B67+1,"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E68" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F68" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G68" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H68" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="19"/>
+      <c r="B69" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C69" s="20"/>
+      <c r="D69" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E69" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F69" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G69" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H69" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="2"/>
+      <c r="B70" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E70" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F70" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G70" s="4" t="str">
+        <f t="shared" ref="G70:G121" si="10">IF(AND($A70&lt;&gt;"",$B70&lt;&gt;""),G69-F70,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="19"/>
+      <c r="B71" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C71" s="20"/>
+      <c r="D71" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E71" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F71" s="21" t="str">
+        <f t="shared" ref="F71:F121" si="11">IF(AND($A71&lt;&gt;"",$B71&lt;&gt;""),D71-E71,"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H71" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="2"/>
+      <c r="B72" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E72" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F72" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G72" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H72" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="19"/>
+      <c r="B73" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C73" s="20"/>
+      <c r="D73" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E73" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F73" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G73" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H73" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="2"/>
+      <c r="B74" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E74" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F74" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G74" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H74" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="19"/>
+      <c r="B75" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C75" s="20"/>
+      <c r="D75" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E75" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F75" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G75" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H75" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2"/>
+      <c r="B76" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E76" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F76" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G76" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H76" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="19"/>
+      <c r="B77" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C77" s="20"/>
+      <c r="D77" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E77" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F77" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G77" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H77" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="2"/>
+      <c r="B78" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E78" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F78" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G78" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H78" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="19"/>
+      <c r="B79" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C79" s="20"/>
+      <c r="D79" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E79" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F79" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G79" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H79" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="2"/>
+      <c r="B80" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E80" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F80" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G80" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H80" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="19"/>
+      <c r="B81" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C81" s="20"/>
+      <c r="D81" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E81" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F81" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G81" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H81" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2"/>
+      <c r="B82" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E82" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F82" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G82" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H82" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="19"/>
+      <c r="B83" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C83" s="20"/>
+      <c r="D83" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E83" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F83" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G83" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H83" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2"/>
+      <c r="B84" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E84" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F84" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G84" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H84" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="19"/>
+      <c r="B85" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C85" s="20"/>
+      <c r="D85" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E85" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F85" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G85" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H85" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="2"/>
+      <c r="B86" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E86" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F86" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G86" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H86" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="19"/>
+      <c r="B87" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C87" s="20"/>
+      <c r="D87" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E87" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F87" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G87" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H87" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="2"/>
+      <c r="B88" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E88" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F88" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G88" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H88" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="19"/>
+      <c r="B89" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C89" s="20"/>
+      <c r="D89" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E89" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F89" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G89" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H89" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="2"/>
+      <c r="B90" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E90" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F90" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G90" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H90" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="19"/>
+      <c r="B91" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C91" s="20"/>
+      <c r="D91" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E91" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F91" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G91" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H91" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2"/>
+      <c r="B92" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E92" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F92" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G92" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H92" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="19"/>
+      <c r="B93" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C93" s="20"/>
+      <c r="D93" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E93" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F93" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G93" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H93" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="2"/>
+      <c r="B94" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E94" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F94" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G94" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H94" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="19"/>
+      <c r="B95" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C95" s="20"/>
+      <c r="D95" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E95" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F95" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G95" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H95" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="2"/>
+      <c r="B96" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E96" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F96" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G96" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H96" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="19"/>
+      <c r="B97" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C97" s="20"/>
+      <c r="D97" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E97" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F97" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G97" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H97" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="2"/>
+      <c r="B98" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E98" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F98" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G98" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H98" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="19"/>
+      <c r="B99" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C99" s="20"/>
+      <c r="D99" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E99" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F99" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G99" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H99" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="2"/>
+      <c r="B100" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E100" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F100" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G100" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H100" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="19"/>
+      <c r="B101" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C101" s="20"/>
+      <c r="D101" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E101" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F101" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G101" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H101" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="2"/>
+      <c r="B102" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E102" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F102" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G102" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H102" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="19"/>
+      <c r="B103" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C103" s="20"/>
+      <c r="D103" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E103" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F103" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G103" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H103" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="2"/>
+      <c r="B104" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E104" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F104" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G104" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H104" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="19"/>
+      <c r="B105" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E105" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F105" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G105" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H105" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="2"/>
+      <c r="B106" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E106" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F106" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G106" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H106" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="19"/>
+      <c r="B107" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C107" s="20"/>
+      <c r="D107" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E107" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F107" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G107" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H107" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="2"/>
+      <c r="B108" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E108" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F108" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G108" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H108" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="19"/>
+      <c r="B109" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E109" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F109" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G109" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H109" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="2"/>
+      <c r="B110" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E110" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F110" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G110" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H110" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="19"/>
+      <c r="B111" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C111" s="20"/>
+      <c r="D111" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E111" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F111" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G111" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H111" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="2"/>
+      <c r="B112" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E112" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F112" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G112" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H112" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="19"/>
+      <c r="B113" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C113" s="20"/>
+      <c r="D113" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E113" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F113" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G113" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H113" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="2"/>
+      <c r="B114" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E114" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F114" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G114" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H114" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="19"/>
+      <c r="B115" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C115" s="20"/>
+      <c r="D115" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E115" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F115" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G115" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H115" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="2"/>
+      <c r="B116" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E116" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F116" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G116" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H116" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="19"/>
+      <c r="B117" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C117" s="20"/>
+      <c r="D117" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E117" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F117" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G117" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H117" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="2"/>
+      <c r="B118" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E118" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F118" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G118" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H118" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="19"/>
+      <c r="B119" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C119" s="20"/>
+      <c r="D119" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E119" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F119" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G119" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H119" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="2"/>
+      <c r="B120" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E120" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F120" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G120" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H120" s="4" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="19"/>
+      <c r="B121" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="C121" s="20"/>
+      <c r="D121" s="21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="E121" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="F121" s="21" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G121" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H121" s="21" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>